--- a/data/industry/CFM/UDIMM.xlsx
+++ b/data/industry/CFM/UDIMM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB66FAF3-415C-466F-9615-B4C5D8DCD067}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA3CB50-713E-4223-88D4-44444804DF41}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DDR4 UDIMM 8GB 3200" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -64,6 +64,9 @@
     <t>UTC+8</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>UTC+8</t>
+  </si>
 </sst>
 </file>
 
@@ -71,10 +74,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="179" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="181" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="182" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="179" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="180" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -137,42 +140,42 @@
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="181" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="182" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
@@ -454,1333 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G28"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="9" style="14"/>
-    <col min="8" max="16384" width="9" style="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="5">
-        <v>45860</v>
-      </c>
-      <c r="B2" s="5">
-        <v>45860</v>
-      </c>
-      <c r="C2" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="13">
-        <v>13.5</v>
-      </c>
-      <c r="F2" s="13">
-        <v>20.3</v>
-      </c>
-      <c r="G2" s="13">
-        <v>15.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="5">
-        <v>45867</v>
-      </c>
-      <c r="B3" s="5">
-        <v>45867</v>
-      </c>
-      <c r="C3" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="13">
-        <v>13.5</v>
-      </c>
-      <c r="F3" s="13">
-        <v>20.3</v>
-      </c>
-      <c r="G3" s="13">
-        <v>15.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="5">
-        <v>45874</v>
-      </c>
-      <c r="B4" s="5">
-        <v>45874</v>
-      </c>
-      <c r="C4" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="13">
-        <v>12</v>
-      </c>
-      <c r="F4" s="13">
-        <v>18.8</v>
-      </c>
-      <c r="G4" s="13">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="5">
-        <v>45881</v>
-      </c>
-      <c r="B5" s="5">
-        <v>45881</v>
-      </c>
-      <c r="C5" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="13">
-        <v>12</v>
-      </c>
-      <c r="F5" s="13">
-        <v>18.8</v>
-      </c>
-      <c r="G5" s="13">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="5">
-        <v>45888</v>
-      </c>
-      <c r="B6" s="5">
-        <v>45888</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="13">
-        <v>12</v>
-      </c>
-      <c r="F6" s="13">
-        <v>18.8</v>
-      </c>
-      <c r="G6" s="13">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="5">
-        <v>45895</v>
-      </c>
-      <c r="B7" s="5">
-        <v>45895</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="13">
-        <v>12.5</v>
-      </c>
-      <c r="F7" s="13">
-        <v>19.3</v>
-      </c>
-      <c r="G7" s="13">
-        <v>14.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="5">
-        <v>45902</v>
-      </c>
-      <c r="B8" s="5">
-        <v>45902</v>
-      </c>
-      <c r="C8" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="13">
-        <v>12.5</v>
-      </c>
-      <c r="F8" s="13">
-        <v>19.3</v>
-      </c>
-      <c r="G8" s="13">
-        <v>14.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="5">
-        <v>45909</v>
-      </c>
-      <c r="B9" s="5">
-        <v>45909</v>
-      </c>
-      <c r="C9" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="13">
-        <v>12.8</v>
-      </c>
-      <c r="F9" s="13">
-        <v>19.600000000000001</v>
-      </c>
-      <c r="G9" s="13">
-        <v>14.8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="5">
-        <v>45916</v>
-      </c>
-      <c r="B10" s="5">
-        <v>45916</v>
-      </c>
-      <c r="C10" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="13">
-        <v>13</v>
-      </c>
-      <c r="F10" s="13">
-        <v>19.8</v>
-      </c>
-      <c r="G10" s="13">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="5">
-        <v>45923</v>
-      </c>
-      <c r="B11" s="5">
-        <v>45923</v>
-      </c>
-      <c r="C11" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="13">
-        <v>13</v>
-      </c>
-      <c r="F11" s="13">
-        <v>19.8</v>
-      </c>
-      <c r="G11" s="13">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="5">
-        <v>45930</v>
-      </c>
-      <c r="B12" s="5">
-        <v>45930</v>
-      </c>
-      <c r="C12" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="13">
-        <v>13</v>
-      </c>
-      <c r="F12" s="13">
-        <v>19.8</v>
-      </c>
-      <c r="G12" s="13">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="5">
-        <v>45944</v>
-      </c>
-      <c r="B13" s="5">
-        <v>45944</v>
-      </c>
-      <c r="C13" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="13">
-        <v>15</v>
-      </c>
-      <c r="F13" s="13">
-        <v>21.8</v>
-      </c>
-      <c r="G13" s="13">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="5">
-        <v>45951</v>
-      </c>
-      <c r="B14" s="5">
-        <v>45951</v>
-      </c>
-      <c r="C14" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="13">
-        <v>15</v>
-      </c>
-      <c r="F14" s="13">
-        <v>21.8</v>
-      </c>
-      <c r="G14" s="13">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="5">
-        <v>45958</v>
-      </c>
-      <c r="B15" s="5">
-        <v>45958</v>
-      </c>
-      <c r="C15" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="13">
-        <v>18</v>
-      </c>
-      <c r="F15" s="13">
-        <v>24.8</v>
-      </c>
-      <c r="G15" s="13">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="5">
-        <v>45965</v>
-      </c>
-      <c r="B16" s="5">
-        <v>45965</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" s="13">
-        <v>18</v>
-      </c>
-      <c r="F16" s="13">
-        <v>24.8</v>
-      </c>
-      <c r="G16" s="13">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="5">
-        <v>45972</v>
-      </c>
-      <c r="B17" s="5">
-        <v>45972</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" s="13">
-        <v>18</v>
-      </c>
-      <c r="F17" s="13">
-        <v>24.8</v>
-      </c>
-      <c r="G17" s="13">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="5">
-        <v>45979</v>
-      </c>
-      <c r="B18" s="5">
-        <v>45979</v>
-      </c>
-      <c r="C18" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" s="13">
-        <v>22</v>
-      </c>
-      <c r="F18" s="13">
-        <v>28.8</v>
-      </c>
-      <c r="G18" s="13">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="5">
-        <v>45986</v>
-      </c>
-      <c r="B19" s="5">
-        <v>45986</v>
-      </c>
-      <c r="C19" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="13">
-        <v>28</v>
-      </c>
-      <c r="F19" s="13">
-        <v>34.799999999999997</v>
-      </c>
-      <c r="G19" s="13">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="5">
-        <v>45993</v>
-      </c>
-      <c r="B20" s="5">
-        <v>45993</v>
-      </c>
-      <c r="C20" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="13">
-        <v>32</v>
-      </c>
-      <c r="F20" s="13">
-        <v>38.799999999999997</v>
-      </c>
-      <c r="G20" s="13">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="5">
-        <v>46000</v>
-      </c>
-      <c r="B21" s="5">
-        <v>46000</v>
-      </c>
-      <c r="C21" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E21" s="13">
-        <v>36</v>
-      </c>
-      <c r="F21" s="13">
-        <v>42.8</v>
-      </c>
-      <c r="G21" s="13">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="5">
-        <v>46007</v>
-      </c>
-      <c r="B22" s="5">
-        <v>46007</v>
-      </c>
-      <c r="C22" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22" s="13">
-        <v>36</v>
-      </c>
-      <c r="F22" s="13">
-        <v>42.8</v>
-      </c>
-      <c r="G22" s="13">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="5">
-        <v>46014</v>
-      </c>
-      <c r="B23" s="5">
-        <v>46014</v>
-      </c>
-      <c r="C23" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" s="13">
-        <v>36</v>
-      </c>
-      <c r="F23" s="13">
-        <v>42.8</v>
-      </c>
-      <c r="G23" s="13">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="5">
-        <v>46021</v>
-      </c>
-      <c r="B24" s="5">
-        <v>46021</v>
-      </c>
-      <c r="C24" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E24" s="13">
-        <v>36</v>
-      </c>
-      <c r="F24" s="13">
-        <v>42.8</v>
-      </c>
-      <c r="G24" s="13">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="5">
-        <v>46028</v>
-      </c>
-      <c r="B25" s="5">
-        <v>46028</v>
-      </c>
-      <c r="C25" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" s="13">
-        <v>43</v>
-      </c>
-      <c r="F25" s="13">
-        <v>50</v>
-      </c>
-      <c r="G25" s="13">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="8">
-        <v>46035</v>
-      </c>
-      <c r="B26" s="8">
-        <v>46035</v>
-      </c>
-      <c r="C26" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E26" s="13">
-        <v>43</v>
-      </c>
-      <c r="F26" s="13">
-        <v>50</v>
-      </c>
-      <c r="G26" s="13">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="8">
-        <v>46042</v>
-      </c>
-      <c r="B27" s="8">
-        <v>46042</v>
-      </c>
-      <c r="C27" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E27" s="13">
-        <v>45</v>
-      </c>
-      <c r="F27" s="13">
-        <v>52</v>
-      </c>
-      <c r="G27" s="13">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="8">
-        <v>46049</v>
-      </c>
-      <c r="B28" s="8">
-        <v>46049</v>
-      </c>
-      <c r="C28" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E28" s="14">
-        <v>48</v>
-      </c>
-      <c r="F28" s="14">
-        <v>55</v>
-      </c>
-      <c r="G28" s="14">
-        <v>50</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{192B0709-717A-492E-9744-92D2DEF39476}">
-  <dimension ref="A1:G28"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="9" style="14"/>
-    <col min="8" max="16384" width="9" style="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="5">
-        <v>45860</v>
-      </c>
-      <c r="B2" s="5">
-        <v>45860</v>
-      </c>
-      <c r="C2" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="13">
-        <v>26</v>
-      </c>
-      <c r="F2" s="13">
-        <v>37.6</v>
-      </c>
-      <c r="G2" s="13">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="5">
-        <v>45867</v>
-      </c>
-      <c r="B3" s="5">
-        <v>45867</v>
-      </c>
-      <c r="C3" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="13">
-        <v>26</v>
-      </c>
-      <c r="F3" s="13">
-        <v>37.6</v>
-      </c>
-      <c r="G3" s="13">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="5">
-        <v>45874</v>
-      </c>
-      <c r="B4" s="5">
-        <v>45874</v>
-      </c>
-      <c r="C4" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="13">
-        <v>25</v>
-      </c>
-      <c r="F4" s="13">
-        <v>36.6</v>
-      </c>
-      <c r="G4" s="13">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="5">
-        <v>45881</v>
-      </c>
-      <c r="B5" s="5">
-        <v>45881</v>
-      </c>
-      <c r="C5" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="13">
-        <v>25</v>
-      </c>
-      <c r="F5" s="13">
-        <v>36.6</v>
-      </c>
-      <c r="G5" s="13">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="5">
-        <v>45888</v>
-      </c>
-      <c r="B6" s="5">
-        <v>45888</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="13">
-        <v>25</v>
-      </c>
-      <c r="F6" s="13">
-        <v>36.6</v>
-      </c>
-      <c r="G6" s="13">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="5">
-        <v>45895</v>
-      </c>
-      <c r="B7" s="5">
-        <v>45895</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="13">
-        <v>25.5</v>
-      </c>
-      <c r="F7" s="13">
-        <v>37.1</v>
-      </c>
-      <c r="G7" s="13">
-        <v>26.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="5">
-        <v>45902</v>
-      </c>
-      <c r="B8" s="5">
-        <v>45902</v>
-      </c>
-      <c r="C8" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="13">
-        <v>25.5</v>
-      </c>
-      <c r="F8" s="13">
-        <v>37.1</v>
-      </c>
-      <c r="G8" s="13">
-        <v>26.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="5">
-        <v>45909</v>
-      </c>
-      <c r="B9" s="5">
-        <v>45909</v>
-      </c>
-      <c r="C9" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="13">
-        <v>25.8</v>
-      </c>
-      <c r="F9" s="13">
-        <v>37.4</v>
-      </c>
-      <c r="G9" s="13">
-        <v>26.8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="5">
-        <v>45916</v>
-      </c>
-      <c r="B10" s="5">
-        <v>45916</v>
-      </c>
-      <c r="C10" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="13">
-        <v>26</v>
-      </c>
-      <c r="F10" s="13">
-        <v>37.6</v>
-      </c>
-      <c r="G10" s="13">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="5">
-        <v>45923</v>
-      </c>
-      <c r="B11" s="5">
-        <v>45923</v>
-      </c>
-      <c r="C11" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="13">
-        <v>26</v>
-      </c>
-      <c r="F11" s="13">
-        <v>37.6</v>
-      </c>
-      <c r="G11" s="13">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="5">
-        <v>45930</v>
-      </c>
-      <c r="B12" s="5">
-        <v>45930</v>
-      </c>
-      <c r="C12" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="13">
-        <v>26</v>
-      </c>
-      <c r="F12" s="13">
-        <v>37.6</v>
-      </c>
-      <c r="G12" s="13">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="5">
-        <v>45944</v>
-      </c>
-      <c r="B13" s="5">
-        <v>45944</v>
-      </c>
-      <c r="C13" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="13">
-        <v>30</v>
-      </c>
-      <c r="F13" s="13">
-        <v>41.6</v>
-      </c>
-      <c r="G13" s="13">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="5">
-        <v>45951</v>
-      </c>
-      <c r="B14" s="5">
-        <v>45951</v>
-      </c>
-      <c r="C14" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="13">
-        <v>30</v>
-      </c>
-      <c r="F14" s="13">
-        <v>41.6</v>
-      </c>
-      <c r="G14" s="13">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="5">
-        <v>45958</v>
-      </c>
-      <c r="B15" s="5">
-        <v>45958</v>
-      </c>
-      <c r="C15" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="13">
-        <v>35</v>
-      </c>
-      <c r="F15" s="13">
-        <v>46.6</v>
-      </c>
-      <c r="G15" s="13">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="5">
-        <v>45965</v>
-      </c>
-      <c r="B16" s="5">
-        <v>45965</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" s="13">
-        <v>35</v>
-      </c>
-      <c r="F16" s="13">
-        <v>46.6</v>
-      </c>
-      <c r="G16" s="13">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="5">
-        <v>45972</v>
-      </c>
-      <c r="B17" s="5">
-        <v>45972</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" s="13">
-        <v>35</v>
-      </c>
-      <c r="F17" s="13">
-        <v>46.6</v>
-      </c>
-      <c r="G17" s="13">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="5">
-        <v>45979</v>
-      </c>
-      <c r="B18" s="5">
-        <v>45979</v>
-      </c>
-      <c r="C18" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" s="13">
-        <v>44</v>
-      </c>
-      <c r="F18" s="13">
-        <v>55.6</v>
-      </c>
-      <c r="G18" s="13">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="5">
-        <v>45986</v>
-      </c>
-      <c r="B19" s="5">
-        <v>45986</v>
-      </c>
-      <c r="C19" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="13">
-        <v>54</v>
-      </c>
-      <c r="F19" s="13">
-        <v>65.599999999999994</v>
-      </c>
-      <c r="G19" s="13">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="5">
-        <v>45993</v>
-      </c>
-      <c r="B20" s="5">
-        <v>45993</v>
-      </c>
-      <c r="C20" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="13">
-        <v>59</v>
-      </c>
-      <c r="F20" s="13">
-        <v>70.599999999999994</v>
-      </c>
-      <c r="G20" s="13">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="5">
-        <v>46000</v>
-      </c>
-      <c r="B21" s="5">
-        <v>46000</v>
-      </c>
-      <c r="C21" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E21" s="13">
-        <v>74</v>
-      </c>
-      <c r="F21" s="13">
-        <v>85.6</v>
-      </c>
-      <c r="G21" s="13">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="5">
-        <v>46007</v>
-      </c>
-      <c r="B22" s="5">
-        <v>46007</v>
-      </c>
-      <c r="C22" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22" s="13">
-        <v>74</v>
-      </c>
-      <c r="F22" s="13">
-        <v>85.6</v>
-      </c>
-      <c r="G22" s="13">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="5">
-        <v>46014</v>
-      </c>
-      <c r="B23" s="5">
-        <v>46014</v>
-      </c>
-      <c r="C23" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" s="13">
-        <v>74</v>
-      </c>
-      <c r="F23" s="13">
-        <v>85.6</v>
-      </c>
-      <c r="G23" s="13">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="5">
-        <v>46021</v>
-      </c>
-      <c r="B24" s="5">
-        <v>46021</v>
-      </c>
-      <c r="C24" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E24" s="13">
-        <v>74</v>
-      </c>
-      <c r="F24" s="13">
-        <v>85.6</v>
-      </c>
-      <c r="G24" s="13">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="5">
-        <v>46028</v>
-      </c>
-      <c r="B25" s="5">
-        <v>46028</v>
-      </c>
-      <c r="C25" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" s="13">
-        <v>84</v>
-      </c>
-      <c r="F25" s="13">
-        <v>95.6</v>
-      </c>
-      <c r="G25" s="13">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="8">
-        <v>46035</v>
-      </c>
-      <c r="B26" s="8">
-        <v>46035</v>
-      </c>
-      <c r="C26" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E26" s="13">
-        <v>84</v>
-      </c>
-      <c r="F26" s="13">
-        <v>95.6</v>
-      </c>
-      <c r="G26" s="13">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="8">
-        <v>46042</v>
-      </c>
-      <c r="B27" s="8">
-        <v>46042</v>
-      </c>
-      <c r="C27" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E27" s="13">
-        <v>89</v>
-      </c>
-      <c r="F27" s="13">
-        <v>100.6</v>
-      </c>
-      <c r="G27" s="13">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="8">
-        <v>46049</v>
-      </c>
-      <c r="B28" s="8">
-        <v>46049</v>
-      </c>
-      <c r="C28" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E28" s="14">
-        <v>94</v>
-      </c>
-      <c r="F28" s="14">
-        <v>105.6</v>
-      </c>
-      <c r="G28" s="14">
-        <v>95</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C33C41F-CAF1-4FD5-8D91-A49D334C85A7}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
@@ -1829,13 +506,13 @@
         <v>7</v>
       </c>
       <c r="E2" s="13">
-        <v>52</v>
+        <v>13.5</v>
       </c>
       <c r="F2" s="13">
-        <v>67</v>
+        <v>20.3</v>
       </c>
       <c r="G2" s="13">
-        <v>57</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -1852,13 +529,13 @@
         <v>7</v>
       </c>
       <c r="E3" s="13">
-        <v>52</v>
+        <v>13.5</v>
       </c>
       <c r="F3" s="13">
-        <v>67</v>
+        <v>20.3</v>
       </c>
       <c r="G3" s="13">
-        <v>57</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -1875,13 +552,13 @@
         <v>7</v>
       </c>
       <c r="E4" s="13">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="F4" s="13">
-        <v>67</v>
+        <v>18.8</v>
       </c>
       <c r="G4" s="13">
-        <v>57</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -1898,13 +575,13 @@
         <v>7</v>
       </c>
       <c r="E5" s="13">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="F5" s="13">
-        <v>67</v>
+        <v>18.8</v>
       </c>
       <c r="G5" s="13">
-        <v>57</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -1921,13 +598,13 @@
         <v>7</v>
       </c>
       <c r="E6" s="13">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="F6" s="13">
-        <v>67</v>
+        <v>18.8</v>
       </c>
       <c r="G6" s="13">
-        <v>57</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -1944,13 +621,13 @@
         <v>7</v>
       </c>
       <c r="E7" s="13">
-        <v>53</v>
+        <v>12.5</v>
       </c>
       <c r="F7" s="13">
-        <v>68</v>
+        <v>19.3</v>
       </c>
       <c r="G7" s="13">
-        <v>58</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -1967,13 +644,13 @@
         <v>7</v>
       </c>
       <c r="E8" s="13">
-        <v>53</v>
+        <v>12.5</v>
       </c>
       <c r="F8" s="13">
-        <v>68</v>
+        <v>19.3</v>
       </c>
       <c r="G8" s="13">
-        <v>58</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -1990,13 +667,13 @@
         <v>7</v>
       </c>
       <c r="E9" s="13">
-        <v>55</v>
+        <v>12.8</v>
       </c>
       <c r="F9" s="13">
-        <v>70</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="G9" s="13">
-        <v>60</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -2013,13 +690,13 @@
         <v>7</v>
       </c>
       <c r="E10" s="13">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="F10" s="13">
-        <v>72</v>
+        <v>19.8</v>
       </c>
       <c r="G10" s="13">
-        <v>62</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -2036,13 +713,13 @@
         <v>7</v>
       </c>
       <c r="E11" s="13">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="F11" s="13">
-        <v>72</v>
+        <v>19.8</v>
       </c>
       <c r="G11" s="13">
-        <v>62</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -2059,13 +736,13 @@
         <v>7</v>
       </c>
       <c r="E12" s="13">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="F12" s="13">
-        <v>72</v>
+        <v>19.8</v>
       </c>
       <c r="G12" s="13">
-        <v>62</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -2082,13 +759,13 @@
         <v>7</v>
       </c>
       <c r="E13" s="13">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="F13" s="13">
-        <v>80</v>
+        <v>21.8</v>
       </c>
       <c r="G13" s="13">
-        <v>70</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -2105,13 +782,13 @@
         <v>7</v>
       </c>
       <c r="E14" s="13">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="F14" s="13">
-        <v>80</v>
+        <v>21.8</v>
       </c>
       <c r="G14" s="13">
-        <v>70</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -2128,13 +805,13 @@
         <v>7</v>
       </c>
       <c r="E15" s="13">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="F15" s="13">
-        <v>90</v>
+        <v>24.8</v>
       </c>
       <c r="G15" s="13">
-        <v>80</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -2151,13 +828,13 @@
         <v>7</v>
       </c>
       <c r="E16" s="13">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="F16" s="13">
-        <v>90</v>
+        <v>24.8</v>
       </c>
       <c r="G16" s="13">
-        <v>80</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -2174,13 +851,13 @@
         <v>7</v>
       </c>
       <c r="E17" s="13">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="F17" s="13">
-        <v>90</v>
+        <v>24.8</v>
       </c>
       <c r="G17" s="13">
-        <v>80</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
@@ -2197,13 +874,13 @@
         <v>7</v>
       </c>
       <c r="E18" s="13">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="F18" s="13">
-        <v>105</v>
+        <v>28.8</v>
       </c>
       <c r="G18" s="13">
-        <v>95</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
@@ -2220,13 +897,13 @@
         <v>7</v>
       </c>
       <c r="E19" s="13">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="F19" s="13">
-        <v>120</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="G19" s="13">
-        <v>110</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
@@ -2243,13 +920,13 @@
         <v>7</v>
       </c>
       <c r="E20" s="13">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="F20" s="13">
-        <v>125</v>
+        <v>38.799999999999997</v>
       </c>
       <c r="G20" s="13">
-        <v>115</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
@@ -2266,13 +943,13 @@
         <v>7</v>
       </c>
       <c r="E21" s="13">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="F21" s="13">
-        <v>135</v>
+        <v>42.8</v>
       </c>
       <c r="G21" s="13">
-        <v>125</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
@@ -2289,13 +966,13 @@
         <v>7</v>
       </c>
       <c r="E22" s="13">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="F22" s="13">
-        <v>135</v>
+        <v>42.8</v>
       </c>
       <c r="G22" s="13">
-        <v>125</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
@@ -2312,13 +989,13 @@
         <v>7</v>
       </c>
       <c r="E23" s="13">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="F23" s="13">
-        <v>135</v>
+        <v>42.8</v>
       </c>
       <c r="G23" s="13">
-        <v>125</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
@@ -2335,13 +1012,13 @@
         <v>7</v>
       </c>
       <c r="E24" s="13">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="F24" s="13">
-        <v>135</v>
+        <v>42.8</v>
       </c>
       <c r="G24" s="13">
-        <v>125</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
@@ -2358,13 +1035,13 @@
         <v>7</v>
       </c>
       <c r="E25" s="13">
-        <v>135</v>
+        <v>43</v>
       </c>
       <c r="F25" s="13">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="G25" s="13">
-        <v>140</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
@@ -2381,13 +1058,13 @@
         <v>7</v>
       </c>
       <c r="E26" s="13">
-        <v>135</v>
+        <v>43</v>
       </c>
       <c r="F26" s="13">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="G26" s="13">
-        <v>140</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
@@ -2404,13 +1081,13 @@
         <v>7</v>
       </c>
       <c r="E27" s="13">
-        <v>155</v>
+        <v>45</v>
       </c>
       <c r="F27" s="13">
-        <v>170</v>
+        <v>52</v>
       </c>
       <c r="G27" s="13">
-        <v>160</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
@@ -2424,16 +1101,131 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E28" s="14">
-        <v>165</v>
+        <v>48</v>
       </c>
       <c r="F28" s="14">
-        <v>180</v>
+        <v>55</v>
       </c>
       <c r="G28" s="14">
-        <v>170</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="14">
+        <v>48</v>
+      </c>
+      <c r="F29" s="14">
+        <v>55</v>
+      </c>
+      <c r="G29" s="14">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="14">
+        <v>48</v>
+      </c>
+      <c r="F30" s="14">
+        <v>55</v>
+      </c>
+      <c r="G30" s="14">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="14">
+        <v>48</v>
+      </c>
+      <c r="F31" s="14">
+        <v>55</v>
+      </c>
+      <c r="G31" s="14">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="14">
+        <v>48</v>
+      </c>
+      <c r="F32" s="14">
+        <v>55</v>
+      </c>
+      <c r="G32" s="14">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="14">
+        <v>58</v>
+      </c>
+      <c r="F33" s="14">
+        <v>65</v>
+      </c>
+      <c r="G33" s="14">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2442,9 +1234,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A33F9B6-7347-4C68-802E-E71624384C9E}">
-  <dimension ref="A1:G28"/>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{192B0709-717A-492E-9744-92D2DEF39476}">
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
@@ -2493,13 +1285,13 @@
         <v>7</v>
       </c>
       <c r="E2" s="13">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F2" s="13">
-        <v>34</v>
+        <v>37.6</v>
       </c>
       <c r="G2" s="13">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -2516,13 +1308,13 @@
         <v>7</v>
       </c>
       <c r="E3" s="13">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F3" s="13">
-        <v>34</v>
+        <v>37.6</v>
       </c>
       <c r="G3" s="13">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -2539,13 +1331,13 @@
         <v>7</v>
       </c>
       <c r="E4" s="13">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F4" s="13">
-        <v>34</v>
+        <v>36.6</v>
       </c>
       <c r="G4" s="13">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -2562,13 +1354,13 @@
         <v>7</v>
       </c>
       <c r="E5" s="13">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F5" s="13">
-        <v>34</v>
+        <v>36.6</v>
       </c>
       <c r="G5" s="13">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -2585,13 +1377,13 @@
         <v>7</v>
       </c>
       <c r="E6" s="13">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F6" s="13">
-        <v>34</v>
+        <v>36.6</v>
       </c>
       <c r="G6" s="13">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -2608,13 +1400,13 @@
         <v>7</v>
       </c>
       <c r="E7" s="13">
-        <v>31</v>
+        <v>25.5</v>
       </c>
       <c r="F7" s="13">
-        <v>35</v>
+        <v>37.1</v>
       </c>
       <c r="G7" s="13">
-        <v>33</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -2631,13 +1423,13 @@
         <v>7</v>
       </c>
       <c r="E8" s="13">
-        <v>31.4</v>
+        <v>25.5</v>
       </c>
       <c r="F8" s="13">
-        <v>35.4</v>
+        <v>37.1</v>
       </c>
       <c r="G8" s="13">
-        <v>33.4</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -2654,13 +1446,13 @@
         <v>7</v>
       </c>
       <c r="E9" s="13">
-        <v>31.8</v>
+        <v>25.8</v>
       </c>
       <c r="F9" s="13">
-        <v>35.799999999999997</v>
+        <v>37.4</v>
       </c>
       <c r="G9" s="13">
-        <v>33.799999999999997</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -2677,13 +1469,13 @@
         <v>7</v>
       </c>
       <c r="E10" s="13">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F10" s="13">
-        <v>36</v>
+        <v>37.6</v>
       </c>
       <c r="G10" s="13">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -2700,13 +1492,13 @@
         <v>7</v>
       </c>
       <c r="E11" s="13">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F11" s="13">
-        <v>36</v>
+        <v>37.6</v>
       </c>
       <c r="G11" s="13">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -2723,13 +1515,13 @@
         <v>7</v>
       </c>
       <c r="E12" s="13">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F12" s="13">
-        <v>36</v>
+        <v>37.6</v>
       </c>
       <c r="G12" s="13">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -2746,13 +1538,13 @@
         <v>7</v>
       </c>
       <c r="E13" s="13">
-        <v>38.6</v>
+        <v>30</v>
       </c>
       <c r="F13" s="13">
-        <v>42.6</v>
+        <v>41.6</v>
       </c>
       <c r="G13" s="13">
-        <v>40.6</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -2769,13 +1561,13 @@
         <v>7</v>
       </c>
       <c r="E14" s="13">
-        <v>38.6</v>
+        <v>30</v>
       </c>
       <c r="F14" s="13">
-        <v>42.6</v>
+        <v>41.6</v>
       </c>
       <c r="G14" s="13">
-        <v>40.6</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -2792,13 +1584,13 @@
         <v>7</v>
       </c>
       <c r="E15" s="13">
-        <v>38.6</v>
+        <v>35</v>
       </c>
       <c r="F15" s="13">
-        <v>42.6</v>
+        <v>46.6</v>
       </c>
       <c r="G15" s="13">
-        <v>40.6</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -2815,13 +1607,13 @@
         <v>7</v>
       </c>
       <c r="E16" s="13">
-        <v>38.6</v>
+        <v>35</v>
       </c>
       <c r="F16" s="13">
-        <v>42.6</v>
+        <v>46.6</v>
       </c>
       <c r="G16" s="13">
-        <v>40.6</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -2838,13 +1630,13 @@
         <v>7</v>
       </c>
       <c r="E17" s="13">
-        <v>38.6</v>
+        <v>35</v>
       </c>
       <c r="F17" s="13">
-        <v>42.6</v>
+        <v>46.6</v>
       </c>
       <c r="G17" s="13">
-        <v>40.6</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
@@ -2861,13 +1653,13 @@
         <v>7</v>
       </c>
       <c r="E18" s="13">
-        <v>38.6</v>
+        <v>44</v>
       </c>
       <c r="F18" s="13">
-        <v>42.6</v>
+        <v>55.6</v>
       </c>
       <c r="G18" s="13">
-        <v>40.6</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
@@ -2884,13 +1676,13 @@
         <v>7</v>
       </c>
       <c r="E19" s="13">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F19" s="13">
-        <v>62</v>
+        <v>65.599999999999994</v>
       </c>
       <c r="G19" s="13">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
@@ -2907,13 +1699,13 @@
         <v>7</v>
       </c>
       <c r="E20" s="13">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="F20" s="13">
-        <v>87</v>
+        <v>70.599999999999994</v>
       </c>
       <c r="G20" s="13">
-        <v>85</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
@@ -2930,13 +1722,13 @@
         <v>7</v>
       </c>
       <c r="E21" s="13">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="F21" s="13">
-        <v>112</v>
+        <v>85.6</v>
       </c>
       <c r="G21" s="13">
-        <v>110</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
@@ -2953,13 +1745,13 @@
         <v>7</v>
       </c>
       <c r="E22" s="13">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="F22" s="13">
-        <v>112</v>
+        <v>85.6</v>
       </c>
       <c r="G22" s="13">
-        <v>110</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
@@ -2976,13 +1768,13 @@
         <v>7</v>
       </c>
       <c r="E23" s="13">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="F23" s="13">
-        <v>112</v>
+        <v>85.6</v>
       </c>
       <c r="G23" s="13">
-        <v>110</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
@@ -2999,13 +1791,13 @@
         <v>7</v>
       </c>
       <c r="E24" s="13">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="F24" s="13">
-        <v>112</v>
+        <v>85.6</v>
       </c>
       <c r="G24" s="13">
-        <v>110</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
@@ -3022,13 +1814,13 @@
         <v>7</v>
       </c>
       <c r="E25" s="13">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="F25" s="13">
-        <v>127</v>
+        <v>95.6</v>
       </c>
       <c r="G25" s="13">
-        <v>125</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
@@ -3045,13 +1837,13 @@
         <v>7</v>
       </c>
       <c r="E26" s="13">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="F26" s="13">
-        <v>127</v>
+        <v>95.6</v>
       </c>
       <c r="G26" s="13">
-        <v>125</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
@@ -3068,13 +1860,13 @@
         <v>7</v>
       </c>
       <c r="E27" s="13">
-        <v>158</v>
+        <v>89</v>
       </c>
       <c r="F27" s="13">
-        <v>162</v>
+        <v>100.6</v>
       </c>
       <c r="G27" s="13">
-        <v>160</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
@@ -3088,16 +1880,131 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E28" s="14">
-        <v>168</v>
+        <v>94</v>
       </c>
       <c r="F28" s="14">
-        <v>172</v>
+        <v>105.6</v>
       </c>
       <c r="G28" s="14">
-        <v>170</v>
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="14">
+        <v>94</v>
+      </c>
+      <c r="F29" s="14">
+        <v>105.6</v>
+      </c>
+      <c r="G29" s="14">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="14">
+        <v>94</v>
+      </c>
+      <c r="F30" s="14">
+        <v>105.6</v>
+      </c>
+      <c r="G30" s="14">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="14">
+        <v>94</v>
+      </c>
+      <c r="F31" s="14">
+        <v>105.6</v>
+      </c>
+      <c r="G31" s="14">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="14">
+        <v>94</v>
+      </c>
+      <c r="F32" s="14">
+        <v>105.6</v>
+      </c>
+      <c r="G32" s="14">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="14">
+        <v>119</v>
+      </c>
+      <c r="F33" s="14">
+        <v>130.6</v>
+      </c>
+      <c r="G33" s="14">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -3106,9 +2013,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55494817-78A6-45DF-9F77-86066DAB20E2}">
-  <dimension ref="A1:G28"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C33C41F-CAF1-4FD5-8D91-A49D334C85A7}">
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
@@ -3157,13 +2064,13 @@
         <v>7</v>
       </c>
       <c r="E2" s="13">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="F2" s="13">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="G2" s="13">
-        <v>35</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -3180,13 +2087,13 @@
         <v>7</v>
       </c>
       <c r="E3" s="13">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="F3" s="13">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="G3" s="13">
-        <v>35</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -3203,13 +2110,13 @@
         <v>7</v>
       </c>
       <c r="E4" s="13">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="F4" s="13">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="G4" s="13">
-        <v>35</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -3226,13 +2133,13 @@
         <v>7</v>
       </c>
       <c r="E5" s="13">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="F5" s="13">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="G5" s="13">
-        <v>35</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -3249,13 +2156,13 @@
         <v>7</v>
       </c>
       <c r="E6" s="13">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="F6" s="13">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="G6" s="13">
-        <v>35</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -3272,13 +2179,13 @@
         <v>7</v>
       </c>
       <c r="E7" s="13">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="F7" s="13">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="G7" s="13">
-        <v>36</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -3295,13 +2202,13 @@
         <v>7</v>
       </c>
       <c r="E8" s="13">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="F8" s="13">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="G8" s="13">
-        <v>37</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -3318,13 +2225,13 @@
         <v>7</v>
       </c>
       <c r="E9" s="13">
-        <v>35.4</v>
+        <v>55</v>
       </c>
       <c r="F9" s="13">
-        <v>39.4</v>
+        <v>70</v>
       </c>
       <c r="G9" s="13">
-        <v>37.4</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -3341,13 +2248,13 @@
         <v>7</v>
       </c>
       <c r="E10" s="13">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="F10" s="13">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="G10" s="13">
-        <v>38</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -3364,13 +2271,13 @@
         <v>7</v>
       </c>
       <c r="E11" s="13">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="F11" s="13">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="G11" s="13">
-        <v>38</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -3387,13 +2294,13 @@
         <v>7</v>
       </c>
       <c r="E12" s="13">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="F12" s="13">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="G12" s="13">
-        <v>38</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -3410,13 +2317,13 @@
         <v>7</v>
       </c>
       <c r="E13" s="13">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="F13" s="13">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="G13" s="13">
-        <v>45</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -3433,13 +2340,13 @@
         <v>7</v>
       </c>
       <c r="E14" s="13">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="F14" s="13">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="G14" s="13">
-        <v>45</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -3456,13 +2363,13 @@
         <v>7</v>
       </c>
       <c r="E15" s="13">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="F15" s="13">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="G15" s="13">
-        <v>45</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -3479,13 +2386,13 @@
         <v>7</v>
       </c>
       <c r="E16" s="13">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="F16" s="13">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="G16" s="13">
-        <v>45</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -3502,13 +2409,13 @@
         <v>7</v>
       </c>
       <c r="E17" s="13">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="F17" s="13">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="G17" s="13">
-        <v>45</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
@@ -3525,13 +2432,13 @@
         <v>7</v>
       </c>
       <c r="E18" s="13">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="F18" s="13">
-        <v>47</v>
+        <v>105</v>
       </c>
       <c r="G18" s="13">
-        <v>45</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
@@ -3548,13 +2455,13 @@
         <v>7</v>
       </c>
       <c r="E19" s="13">
-        <v>63</v>
+        <v>105</v>
       </c>
       <c r="F19" s="13">
-        <v>67</v>
+        <v>120</v>
       </c>
       <c r="G19" s="13">
-        <v>65</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
@@ -3571,13 +2478,13 @@
         <v>7</v>
       </c>
       <c r="E20" s="13">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="F20" s="13">
-        <v>92</v>
+        <v>125</v>
       </c>
       <c r="G20" s="13">
-        <v>90</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
@@ -3594,13 +2501,13 @@
         <v>7</v>
       </c>
       <c r="E21" s="13">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F21" s="13">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="G21" s="13">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
@@ -3617,13 +2524,13 @@
         <v>7</v>
       </c>
       <c r="E22" s="13">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F22" s="13">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="G22" s="13">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
@@ -3640,13 +2547,13 @@
         <v>7</v>
       </c>
       <c r="E23" s="13">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F23" s="13">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="G23" s="13">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
@@ -3663,13 +2570,13 @@
         <v>7</v>
       </c>
       <c r="E24" s="13">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F24" s="13">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="G24" s="13">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
@@ -3686,13 +2593,13 @@
         <v>7</v>
       </c>
       <c r="E25" s="13">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="F25" s="13">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="G25" s="13">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
@@ -3709,13 +2616,13 @@
         <v>7</v>
       </c>
       <c r="E26" s="13">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="F26" s="13">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="G26" s="13">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
@@ -3732,13 +2639,13 @@
         <v>7</v>
       </c>
       <c r="E27" s="13">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="F27" s="13">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G27" s="13">
-        <v>170</v>
+        <v>160</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
@@ -3752,7 +2659,1565 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="E28" s="14">
+        <v>165</v>
+      </c>
+      <c r="F28" s="14">
+        <v>180</v>
+      </c>
+      <c r="G28" s="14">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="14">
+        <v>165</v>
+      </c>
+      <c r="F29" s="14">
+        <v>180</v>
+      </c>
+      <c r="G29" s="14">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="14">
+        <v>165</v>
+      </c>
+      <c r="F30" s="14">
+        <v>180</v>
+      </c>
+      <c r="G30" s="14">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="14">
+        <v>165</v>
+      </c>
+      <c r="F31" s="14">
+        <v>180</v>
+      </c>
+      <c r="G31" s="14">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="14">
+        <v>165</v>
+      </c>
+      <c r="F32" s="14">
+        <v>180</v>
+      </c>
+      <c r="G32" s="14">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="14">
+        <v>215</v>
+      </c>
+      <c r="F33" s="14">
+        <v>230</v>
+      </c>
+      <c r="G33" s="14">
+        <v>220</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A33F9B6-7347-4C68-802E-E71624384C9E}">
+  <dimension ref="A1:G33"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" style="14"/>
+    <col min="7" max="7" width="11.25" style="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="5">
+        <v>45860</v>
+      </c>
+      <c r="B2" s="5">
+        <v>45860</v>
+      </c>
+      <c r="C2" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="13">
+        <v>30</v>
+      </c>
+      <c r="F2" s="13">
+        <v>34</v>
+      </c>
+      <c r="G2" s="13">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="5">
+        <v>45867</v>
+      </c>
+      <c r="B3" s="5">
+        <v>45867</v>
+      </c>
+      <c r="C3" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="13">
+        <v>30</v>
+      </c>
+      <c r="F3" s="13">
+        <v>34</v>
+      </c>
+      <c r="G3" s="13">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="5">
+        <v>45874</v>
+      </c>
+      <c r="B4" s="5">
+        <v>45874</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="13">
+        <v>30</v>
+      </c>
+      <c r="F4" s="13">
+        <v>34</v>
+      </c>
+      <c r="G4" s="13">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="5">
+        <v>45881</v>
+      </c>
+      <c r="B5" s="5">
+        <v>45881</v>
+      </c>
+      <c r="C5" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="13">
+        <v>30</v>
+      </c>
+      <c r="F5" s="13">
+        <v>34</v>
+      </c>
+      <c r="G5" s="13">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="5">
+        <v>45888</v>
+      </c>
+      <c r="B6" s="5">
+        <v>45888</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="13">
+        <v>30</v>
+      </c>
+      <c r="F6" s="13">
+        <v>34</v>
+      </c>
+      <c r="G6" s="13">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="5">
+        <v>45895</v>
+      </c>
+      <c r="B7" s="5">
+        <v>45895</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="13">
+        <v>31</v>
+      </c>
+      <c r="F7" s="13">
+        <v>35</v>
+      </c>
+      <c r="G7" s="13">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="5">
+        <v>45902</v>
+      </c>
+      <c r="B8" s="5">
+        <v>45902</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="13">
+        <v>31.4</v>
+      </c>
+      <c r="F8" s="13">
+        <v>35.4</v>
+      </c>
+      <c r="G8" s="13">
+        <v>33.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="5">
+        <v>45909</v>
+      </c>
+      <c r="B9" s="5">
+        <v>45909</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="13">
+        <v>31.8</v>
+      </c>
+      <c r="F9" s="13">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="G9" s="13">
+        <v>33.799999999999997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="5">
+        <v>45916</v>
+      </c>
+      <c r="B10" s="5">
+        <v>45916</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="13">
+        <v>32</v>
+      </c>
+      <c r="F10" s="13">
+        <v>36</v>
+      </c>
+      <c r="G10" s="13">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="5">
+        <v>45923</v>
+      </c>
+      <c r="B11" s="5">
+        <v>45923</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="13">
+        <v>32</v>
+      </c>
+      <c r="F11" s="13">
+        <v>36</v>
+      </c>
+      <c r="G11" s="13">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="5">
+        <v>45930</v>
+      </c>
+      <c r="B12" s="5">
+        <v>45930</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="13">
+        <v>32</v>
+      </c>
+      <c r="F12" s="13">
+        <v>36</v>
+      </c>
+      <c r="G12" s="13">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="5">
+        <v>45944</v>
+      </c>
+      <c r="B13" s="5">
+        <v>45944</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="13">
+        <v>38.6</v>
+      </c>
+      <c r="F13" s="13">
+        <v>42.6</v>
+      </c>
+      <c r="G13" s="13">
+        <v>40.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="5">
+        <v>45951</v>
+      </c>
+      <c r="B14" s="5">
+        <v>45951</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="13">
+        <v>38.6</v>
+      </c>
+      <c r="F14" s="13">
+        <v>42.6</v>
+      </c>
+      <c r="G14" s="13">
+        <v>40.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="5">
+        <v>45958</v>
+      </c>
+      <c r="B15" s="5">
+        <v>45958</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="13">
+        <v>38.6</v>
+      </c>
+      <c r="F15" s="13">
+        <v>42.6</v>
+      </c>
+      <c r="G15" s="13">
+        <v>40.6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="5">
+        <v>45965</v>
+      </c>
+      <c r="B16" s="5">
+        <v>45965</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="13">
+        <v>38.6</v>
+      </c>
+      <c r="F16" s="13">
+        <v>42.6</v>
+      </c>
+      <c r="G16" s="13">
+        <v>40.6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="5">
+        <v>45972</v>
+      </c>
+      <c r="B17" s="5">
+        <v>45972</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="13">
+        <v>38.6</v>
+      </c>
+      <c r="F17" s="13">
+        <v>42.6</v>
+      </c>
+      <c r="G17" s="13">
+        <v>40.6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="5">
+        <v>45979</v>
+      </c>
+      <c r="B18" s="5">
+        <v>45979</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="13">
+        <v>38.6</v>
+      </c>
+      <c r="F18" s="13">
+        <v>42.6</v>
+      </c>
+      <c r="G18" s="13">
+        <v>40.6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="5">
+        <v>45986</v>
+      </c>
+      <c r="B19" s="5">
+        <v>45986</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="13">
+        <v>58</v>
+      </c>
+      <c r="F19" s="13">
+        <v>62</v>
+      </c>
+      <c r="G19" s="13">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="5">
+        <v>45993</v>
+      </c>
+      <c r="B20" s="5">
+        <v>45993</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="13">
+        <v>83</v>
+      </c>
+      <c r="F20" s="13">
+        <v>87</v>
+      </c>
+      <c r="G20" s="13">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="5">
+        <v>46000</v>
+      </c>
+      <c r="B21" s="5">
+        <v>46000</v>
+      </c>
+      <c r="C21" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="13">
+        <v>108</v>
+      </c>
+      <c r="F21" s="13">
+        <v>112</v>
+      </c>
+      <c r="G21" s="13">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" s="5">
+        <v>46007</v>
+      </c>
+      <c r="B22" s="5">
+        <v>46007</v>
+      </c>
+      <c r="C22" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="13">
+        <v>108</v>
+      </c>
+      <c r="F22" s="13">
+        <v>112</v>
+      </c>
+      <c r="G22" s="13">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="5">
+        <v>46014</v>
+      </c>
+      <c r="B23" s="5">
+        <v>46014</v>
+      </c>
+      <c r="C23" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="13">
+        <v>108</v>
+      </c>
+      <c r="F23" s="13">
+        <v>112</v>
+      </c>
+      <c r="G23" s="13">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" s="5">
+        <v>46021</v>
+      </c>
+      <c r="B24" s="5">
+        <v>46021</v>
+      </c>
+      <c r="C24" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="13">
+        <v>108</v>
+      </c>
+      <c r="F24" s="13">
+        <v>112</v>
+      </c>
+      <c r="G24" s="13">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="5">
+        <v>46028</v>
+      </c>
+      <c r="B25" s="5">
+        <v>46028</v>
+      </c>
+      <c r="C25" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="13">
+        <v>123</v>
+      </c>
+      <c r="F25" s="13">
+        <v>127</v>
+      </c>
+      <c r="G25" s="13">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" s="8">
+        <v>46035</v>
+      </c>
+      <c r="B26" s="8">
+        <v>46035</v>
+      </c>
+      <c r="C26" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="13">
+        <v>123</v>
+      </c>
+      <c r="F26" s="13">
+        <v>127</v>
+      </c>
+      <c r="G26" s="13">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" s="8">
+        <v>46042</v>
+      </c>
+      <c r="B27" s="8">
+        <v>46042</v>
+      </c>
+      <c r="C27" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" s="13">
+        <v>158</v>
+      </c>
+      <c r="F27" s="13">
+        <v>162</v>
+      </c>
+      <c r="G27" s="13">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" s="8">
+        <v>46049</v>
+      </c>
+      <c r="B28" s="8">
+        <v>46049</v>
+      </c>
+      <c r="C28" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="14">
+        <v>168</v>
+      </c>
+      <c r="F28" s="14">
+        <v>172</v>
+      </c>
+      <c r="G28" s="14">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="14">
+        <v>168</v>
+      </c>
+      <c r="F29" s="14">
+        <v>172</v>
+      </c>
+      <c r="G29" s="14">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="14">
+        <v>168</v>
+      </c>
+      <c r="F30" s="14">
+        <v>172</v>
+      </c>
+      <c r="G30" s="14">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="14">
+        <v>168</v>
+      </c>
+      <c r="F31" s="14">
+        <v>172</v>
+      </c>
+      <c r="G31" s="14">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="14">
+        <v>168</v>
+      </c>
+      <c r="F32" s="14">
+        <v>172</v>
+      </c>
+      <c r="G32" s="14">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="14">
+        <v>188</v>
+      </c>
+      <c r="F33" s="14">
+        <v>192</v>
+      </c>
+      <c r="G33" s="14">
+        <v>190</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55494817-78A6-45DF-9F77-86066DAB20E2}">
+  <dimension ref="A1:G33"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" style="14"/>
+    <col min="7" max="7" width="11.25" style="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="5">
+        <v>45860</v>
+      </c>
+      <c r="B2" s="5">
+        <v>45860</v>
+      </c>
+      <c r="C2" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="13">
+        <v>33</v>
+      </c>
+      <c r="F2" s="13">
+        <v>37</v>
+      </c>
+      <c r="G2" s="13">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="5">
+        <v>45867</v>
+      </c>
+      <c r="B3" s="5">
+        <v>45867</v>
+      </c>
+      <c r="C3" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="13">
+        <v>33</v>
+      </c>
+      <c r="F3" s="13">
+        <v>37</v>
+      </c>
+      <c r="G3" s="13">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="5">
+        <v>45874</v>
+      </c>
+      <c r="B4" s="5">
+        <v>45874</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="13">
+        <v>33</v>
+      </c>
+      <c r="F4" s="13">
+        <v>37</v>
+      </c>
+      <c r="G4" s="13">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="5">
+        <v>45881</v>
+      </c>
+      <c r="B5" s="5">
+        <v>45881</v>
+      </c>
+      <c r="C5" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="13">
+        <v>33</v>
+      </c>
+      <c r="F5" s="13">
+        <v>37</v>
+      </c>
+      <c r="G5" s="13">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="5">
+        <v>45888</v>
+      </c>
+      <c r="B6" s="5">
+        <v>45888</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="13">
+        <v>33</v>
+      </c>
+      <c r="F6" s="13">
+        <v>37</v>
+      </c>
+      <c r="G6" s="13">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="5">
+        <v>45895</v>
+      </c>
+      <c r="B7" s="5">
+        <v>45895</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="13">
+        <v>34</v>
+      </c>
+      <c r="F7" s="13">
+        <v>38</v>
+      </c>
+      <c r="G7" s="13">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="5">
+        <v>45902</v>
+      </c>
+      <c r="B8" s="5">
+        <v>45902</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="13">
+        <v>35</v>
+      </c>
+      <c r="F8" s="13">
+        <v>39</v>
+      </c>
+      <c r="G8" s="13">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="5">
+        <v>45909</v>
+      </c>
+      <c r="B9" s="5">
+        <v>45909</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="13">
+        <v>35.4</v>
+      </c>
+      <c r="F9" s="13">
+        <v>39.4</v>
+      </c>
+      <c r="G9" s="13">
+        <v>37.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="5">
+        <v>45916</v>
+      </c>
+      <c r="B10" s="5">
+        <v>45916</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="13">
+        <v>36</v>
+      </c>
+      <c r="F10" s="13">
+        <v>40</v>
+      </c>
+      <c r="G10" s="13">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="5">
+        <v>45923</v>
+      </c>
+      <c r="B11" s="5">
+        <v>45923</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="13">
+        <v>36</v>
+      </c>
+      <c r="F11" s="13">
+        <v>40</v>
+      </c>
+      <c r="G11" s="13">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="5">
+        <v>45930</v>
+      </c>
+      <c r="B12" s="5">
+        <v>45930</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="13">
+        <v>36</v>
+      </c>
+      <c r="F12" s="13">
+        <v>40</v>
+      </c>
+      <c r="G12" s="13">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="5">
+        <v>45944</v>
+      </c>
+      <c r="B13" s="5">
+        <v>45944</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="13">
+        <v>43</v>
+      </c>
+      <c r="F13" s="13">
+        <v>47</v>
+      </c>
+      <c r="G13" s="13">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="5">
+        <v>45951</v>
+      </c>
+      <c r="B14" s="5">
+        <v>45951</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="13">
+        <v>43</v>
+      </c>
+      <c r="F14" s="13">
+        <v>47</v>
+      </c>
+      <c r="G14" s="13">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="5">
+        <v>45958</v>
+      </c>
+      <c r="B15" s="5">
+        <v>45958</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="13">
+        <v>43</v>
+      </c>
+      <c r="F15" s="13">
+        <v>47</v>
+      </c>
+      <c r="G15" s="13">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="5">
+        <v>45965</v>
+      </c>
+      <c r="B16" s="5">
+        <v>45965</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="13">
+        <v>43</v>
+      </c>
+      <c r="F16" s="13">
+        <v>47</v>
+      </c>
+      <c r="G16" s="13">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="5">
+        <v>45972</v>
+      </c>
+      <c r="B17" s="5">
+        <v>45972</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="13">
+        <v>43</v>
+      </c>
+      <c r="F17" s="13">
+        <v>47</v>
+      </c>
+      <c r="G17" s="13">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="5">
+        <v>45979</v>
+      </c>
+      <c r="B18" s="5">
+        <v>45979</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="13">
+        <v>43</v>
+      </c>
+      <c r="F18" s="13">
+        <v>47</v>
+      </c>
+      <c r="G18" s="13">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="5">
+        <v>45986</v>
+      </c>
+      <c r="B19" s="5">
+        <v>45986</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="13">
+        <v>63</v>
+      </c>
+      <c r="F19" s="13">
+        <v>67</v>
+      </c>
+      <c r="G19" s="13">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="5">
+        <v>45993</v>
+      </c>
+      <c r="B20" s="5">
+        <v>45993</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="13">
+        <v>88</v>
+      </c>
+      <c r="F20" s="13">
+        <v>92</v>
+      </c>
+      <c r="G20" s="13">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="5">
+        <v>46000</v>
+      </c>
+      <c r="B21" s="5">
+        <v>46000</v>
+      </c>
+      <c r="C21" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="13">
+        <v>118</v>
+      </c>
+      <c r="F21" s="13">
+        <v>122</v>
+      </c>
+      <c r="G21" s="13">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" s="5">
+        <v>46007</v>
+      </c>
+      <c r="B22" s="5">
+        <v>46007</v>
+      </c>
+      <c r="C22" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="13">
+        <v>118</v>
+      </c>
+      <c r="F22" s="13">
+        <v>122</v>
+      </c>
+      <c r="G22" s="13">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="5">
+        <v>46014</v>
+      </c>
+      <c r="B23" s="5">
+        <v>46014</v>
+      </c>
+      <c r="C23" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="13">
+        <v>118</v>
+      </c>
+      <c r="F23" s="13">
+        <v>122</v>
+      </c>
+      <c r="G23" s="13">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" s="5">
+        <v>46021</v>
+      </c>
+      <c r="B24" s="5">
+        <v>46021</v>
+      </c>
+      <c r="C24" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="13">
+        <v>118</v>
+      </c>
+      <c r="F24" s="13">
+        <v>122</v>
+      </c>
+      <c r="G24" s="13">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="5">
+        <v>46028</v>
+      </c>
+      <c r="B25" s="5">
+        <v>46028</v>
+      </c>
+      <c r="C25" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="13">
+        <v>143</v>
+      </c>
+      <c r="F25" s="13">
+        <v>147</v>
+      </c>
+      <c r="G25" s="13">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" s="8">
+        <v>46035</v>
+      </c>
+      <c r="B26" s="8">
+        <v>46035</v>
+      </c>
+      <c r="C26" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="13">
+        <v>143</v>
+      </c>
+      <c r="F26" s="13">
+        <v>147</v>
+      </c>
+      <c r="G26" s="13">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" s="8">
+        <v>46042</v>
+      </c>
+      <c r="B27" s="8">
+        <v>46042</v>
+      </c>
+      <c r="C27" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" s="13">
+        <v>167</v>
+      </c>
+      <c r="F27" s="13">
+        <v>172</v>
+      </c>
+      <c r="G27" s="13">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" s="8">
+        <v>46049</v>
+      </c>
+      <c r="B28" s="8">
+        <v>46049</v>
+      </c>
+      <c r="C28" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>8</v>
       </c>
       <c r="E28" s="14">
         <v>177</v>
@@ -3762,6 +4227,121 @@
       </c>
       <c r="G28" s="14">
         <v>180</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="14">
+        <v>177</v>
+      </c>
+      <c r="F29" s="14">
+        <v>182</v>
+      </c>
+      <c r="G29" s="14">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="14">
+        <v>177</v>
+      </c>
+      <c r="F30" s="14">
+        <v>182</v>
+      </c>
+      <c r="G30" s="14">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="14">
+        <v>177</v>
+      </c>
+      <c r="F31" s="14">
+        <v>182</v>
+      </c>
+      <c r="G31" s="14">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="14">
+        <v>177</v>
+      </c>
+      <c r="F32" s="14">
+        <v>182</v>
+      </c>
+      <c r="G32" s="14">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="14">
+        <v>197</v>
+      </c>
+      <c r="F33" s="14">
+        <v>202</v>
+      </c>
+      <c r="G33" s="14">
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -3772,7 +4352,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B6A378-E9BB-4F97-B1F3-B76BB8A3CEFF}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
@@ -4416,7 +4996,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E28" s="11">
         <v>267</v>
@@ -4426,6 +5006,121 @@
       </c>
       <c r="G28" s="11">
         <v>270</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="11">
+        <v>267</v>
+      </c>
+      <c r="F29" s="11">
+        <v>273</v>
+      </c>
+      <c r="G29" s="11">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="11">
+        <v>267</v>
+      </c>
+      <c r="F30" s="11">
+        <v>273</v>
+      </c>
+      <c r="G30" s="11">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="11">
+        <v>267</v>
+      </c>
+      <c r="F31" s="11">
+        <v>273</v>
+      </c>
+      <c r="G31" s="11">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="11">
+        <v>267</v>
+      </c>
+      <c r="F32" s="11">
+        <v>273</v>
+      </c>
+      <c r="G32" s="11">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="11">
+        <v>317</v>
+      </c>
+      <c r="F33" s="11">
+        <v>323</v>
+      </c>
+      <c r="G33" s="11">
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -4436,7 +5131,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D2BE078-281B-4EE8-A7DD-0530E85C5130}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
@@ -5080,7 +5775,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E28" s="11">
         <v>277</v>
@@ -5090,6 +5785,121 @@
       </c>
       <c r="G28" s="11">
         <v>280</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="11">
+        <v>277</v>
+      </c>
+      <c r="F29" s="11">
+        <v>283</v>
+      </c>
+      <c r="G29" s="11">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="11">
+        <v>277</v>
+      </c>
+      <c r="F30" s="11">
+        <v>283</v>
+      </c>
+      <c r="G30" s="11">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="11">
+        <v>277</v>
+      </c>
+      <c r="F31" s="11">
+        <v>283</v>
+      </c>
+      <c r="G31" s="11">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="11">
+        <v>277</v>
+      </c>
+      <c r="F32" s="11">
+        <v>283</v>
+      </c>
+      <c r="G32" s="11">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="11">
+        <v>327</v>
+      </c>
+      <c r="F33" s="11">
+        <v>333</v>
+      </c>
+      <c r="G33" s="11">
+        <v>330</v>
       </c>
     </row>
   </sheetData>

--- a/data/industry/CFM/UDIMM.xlsx
+++ b/data/industry/CFM/UDIMM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA3CB50-713E-4223-88D4-44444804DF41}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6393E40F-7B17-4CFB-86CF-8FA32BE1C378}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -457,7 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
@@ -1228,6 +1228,52 @@
         <v>60</v>
       </c>
     </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="8">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="8">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="14">
+        <v>58</v>
+      </c>
+      <c r="F34" s="14">
+        <v>65</v>
+      </c>
+      <c r="G34" s="14">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="8">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="8">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="14">
+        <v>58</v>
+      </c>
+      <c r="F35" s="14">
+        <v>65</v>
+      </c>
+      <c r="G35" s="14">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1236,7 +1282,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{192B0709-717A-492E-9744-92D2DEF39476}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
@@ -2007,6 +2053,52 @@
         <v>120</v>
       </c>
     </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="8">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="8">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="14">
+        <v>119</v>
+      </c>
+      <c r="F34" s="14">
+        <v>130.6</v>
+      </c>
+      <c r="G34" s="14">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="8">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="8">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="14">
+        <v>119</v>
+      </c>
+      <c r="F35" s="14">
+        <v>130.6</v>
+      </c>
+      <c r="G35" s="14">
+        <v>120</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2015,7 +2107,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C33C41F-CAF1-4FD5-8D91-A49D334C85A7}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
@@ -2786,6 +2878,52 @@
         <v>220</v>
       </c>
     </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="8">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="8">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="14">
+        <v>215</v>
+      </c>
+      <c r="F34" s="14">
+        <v>230</v>
+      </c>
+      <c r="G34" s="14">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="8">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="8">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="14">
+        <v>215</v>
+      </c>
+      <c r="F35" s="14">
+        <v>230</v>
+      </c>
+      <c r="G35" s="14">
+        <v>220</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2794,7 +2932,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A33F9B6-7347-4C68-802E-E71624384C9E}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
@@ -3565,6 +3703,52 @@
         <v>190</v>
       </c>
     </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="8">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="8">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="14">
+        <v>188</v>
+      </c>
+      <c r="F34" s="14">
+        <v>192</v>
+      </c>
+      <c r="G34" s="14">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="8">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="8">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="14">
+        <v>188</v>
+      </c>
+      <c r="F35" s="14">
+        <v>192</v>
+      </c>
+      <c r="G35" s="14">
+        <v>190</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3573,7 +3757,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55494817-78A6-45DF-9F77-86066DAB20E2}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
@@ -4344,6 +4528,52 @@
         <v>200</v>
       </c>
     </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="8">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="8">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="14">
+        <v>197</v>
+      </c>
+      <c r="F34" s="14">
+        <v>202</v>
+      </c>
+      <c r="G34" s="14">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="8">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="8">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="14">
+        <v>197</v>
+      </c>
+      <c r="F35" s="14">
+        <v>202</v>
+      </c>
+      <c r="G35" s="14">
+        <v>200</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4352,7 +4582,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B6A378-E9BB-4F97-B1F3-B76BB8A3CEFF}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
@@ -5123,6 +5353,52 @@
         <v>320</v>
       </c>
     </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="8">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="8">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="11">
+        <v>317</v>
+      </c>
+      <c r="F34" s="11">
+        <v>323</v>
+      </c>
+      <c r="G34" s="11">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="8">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="8">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="11">
+        <v>317</v>
+      </c>
+      <c r="F35" s="11">
+        <v>323</v>
+      </c>
+      <c r="G35" s="11">
+        <v>320</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5131,7 +5407,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D2BE078-281B-4EE8-A7DD-0530E85C5130}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
@@ -5902,6 +6178,52 @@
         <v>330</v>
       </c>
     </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="8">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="8">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="11">
+        <v>327</v>
+      </c>
+      <c r="F34" s="11">
+        <v>333</v>
+      </c>
+      <c r="G34" s="11">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="8">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="8">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="11">
+        <v>327</v>
+      </c>
+      <c r="F35" s="11">
+        <v>333</v>
+      </c>
+      <c r="G35" s="11">
+        <v>330</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/industry/CFM/UDIMM.xlsx
+++ b/data/industry/CFM/UDIMM.xlsx
@@ -1,25 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1297D31F-E806-4637-B1B4-2E30520E19B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E55B6EF2-E80D-4F9F-AAF2-5612D03481E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DDR4 UDIMM 8GB 3200" sheetId="1" r:id="rId1"/>
     <sheet name="DDR4 UDIMM 16GB 3200" sheetId="2" r:id="rId2"/>
     <sheet name="DDR4 UDIMM 32GB 3200" sheetId="3" r:id="rId3"/>
-    <sheet name="DDR5 UDIMM 16GB 5600" sheetId="4" r:id="rId4"/>
-    <sheet name="DDR5 UDIMM 16GB 6000" sheetId="5" r:id="rId5"/>
-    <sheet name="DDR5 UDIMM 32GB 5600" sheetId="6" r:id="rId6"/>
-    <sheet name="DDR5 UDIMM 32GB 6000" sheetId="7" r:id="rId7"/>
+    <sheet name="DDR5 UDIMM 8GB 5600" sheetId="8" r:id="rId4"/>
+    <sheet name="DDR5 UDIMM 8GB 6000" sheetId="9" r:id="rId5"/>
+    <sheet name="DDR5 UDIMM 16GB 5600" sheetId="4" r:id="rId6"/>
+    <sheet name="DDR5 UDIMM 16GB 6000" sheetId="5" r:id="rId7"/>
+    <sheet name="DDR5 UDIMM 32GB 5600" sheetId="6" r:id="rId8"/>
+    <sheet name="DDR5 UDIMM 32GB 6000" sheetId="7" r:id="rId9"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -73,24 +75,24 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="179" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="180" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -103,7 +105,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -113,6 +115,14 @@
       <color theme="1"/>
       <name val="Verdana"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -134,55 +144,88 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
@@ -464,19 +507,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="11.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -499,7 +542,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="5">
         <v>45860</v>
       </c>
@@ -522,7 +565,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="5">
         <v>45867</v>
       </c>
@@ -545,7 +588,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="5">
         <v>45874</v>
       </c>
@@ -568,7 +611,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="5">
         <v>45881</v>
       </c>
@@ -591,7 +634,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="5">
         <v>45888</v>
       </c>
@@ -614,7 +657,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="5">
         <v>45895</v>
       </c>
@@ -637,7 +680,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="5">
         <v>45902</v>
       </c>
@@ -660,7 +703,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="5">
         <v>45909</v>
       </c>
@@ -683,7 +726,7 @@
         <v>14.8</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="5">
         <v>45916</v>
       </c>
@@ -706,7 +749,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="5">
         <v>45923</v>
       </c>
@@ -729,7 +772,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="5">
         <v>45930</v>
       </c>
@@ -752,7 +795,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="5">
         <v>45944</v>
       </c>
@@ -775,7 +818,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="5">
         <v>45951</v>
       </c>
@@ -798,7 +841,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="5">
         <v>45958</v>
       </c>
@@ -821,7 +864,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="5">
         <v>45965</v>
       </c>
@@ -844,7 +887,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="5">
         <v>45972</v>
       </c>
@@ -867,7 +910,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="5">
         <v>45979</v>
       </c>
@@ -890,7 +933,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="5">
         <v>45986</v>
       </c>
@@ -913,7 +956,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="5">
         <v>45993</v>
       </c>
@@ -936,7 +979,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="5">
         <v>46000</v>
       </c>
@@ -959,7 +1002,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="5">
         <v>46007</v>
       </c>
@@ -982,7 +1025,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="5">
         <v>46014</v>
       </c>
@@ -1005,7 +1048,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="5">
         <v>46021</v>
       </c>
@@ -1028,7 +1071,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="5">
         <v>46028</v>
       </c>
@@ -1051,7 +1094,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="8">
         <v>46035</v>
       </c>
@@ -1074,7 +1117,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="8">
         <v>46042</v>
       </c>
@@ -1097,7 +1140,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="8">
         <v>46049</v>
       </c>
@@ -1120,7 +1163,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="8">
         <v>46056</v>
       </c>
@@ -1143,7 +1186,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="8">
         <v>46063</v>
       </c>
@@ -1166,7 +1209,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="8">
         <v>46077</v>
       </c>
@@ -1189,7 +1232,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="8">
         <v>46084</v>
       </c>
@@ -1212,7 +1255,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="8">
         <v>46091</v>
       </c>
@@ -1235,7 +1278,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="8">
         <v>46098</v>
       </c>
@@ -1258,7 +1301,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="8">
         <v>46105</v>
       </c>
@@ -1281,7 +1324,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="8">
         <v>46112</v>
       </c>
@@ -1304,7 +1347,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="8">
         <v>46119</v>
       </c>
@@ -1327,7 +1370,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="8">
         <v>46126</v>
       </c>
@@ -1350,7 +1393,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="8">
         <v>46133</v>
       </c>
@@ -1371,6 +1414,144 @@
       </c>
       <c r="G39" s="11">
         <v>42</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="11">
+        <v>38</v>
+      </c>
+      <c r="F40" s="11">
+        <v>45</v>
+      </c>
+      <c r="G40" s="11">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="11">
+        <v>36</v>
+      </c>
+      <c r="F41" s="11">
+        <v>43</v>
+      </c>
+      <c r="G41" s="11">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="11">
+        <v>36</v>
+      </c>
+      <c r="F42" s="11">
+        <v>43</v>
+      </c>
+      <c r="G42" s="11">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="11">
+        <v>36</v>
+      </c>
+      <c r="F43" s="11">
+        <v>43</v>
+      </c>
+      <c r="G43" s="11">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="11">
+        <v>36</v>
+      </c>
+      <c r="F44" s="11">
+        <v>43</v>
+      </c>
+      <c r="G44" s="11">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="11">
+        <v>36</v>
+      </c>
+      <c r="F45" s="11">
+        <v>43</v>
+      </c>
+      <c r="G45" s="11">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1381,20 +1562,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{192B0709-717A-492E-9744-92D2DEF39476}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="11" customWidth="1"/>
     <col min="6" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="11.19921875" style="11" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="11" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1417,7 +1598,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="5">
         <v>45860</v>
       </c>
@@ -1440,7 +1621,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="5">
         <v>45867</v>
       </c>
@@ -1463,7 +1644,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="5">
         <v>45874</v>
       </c>
@@ -1486,7 +1667,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="5">
         <v>45881</v>
       </c>
@@ -1509,7 +1690,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="5">
         <v>45888</v>
       </c>
@@ -1532,7 +1713,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="5">
         <v>45895</v>
       </c>
@@ -1555,7 +1736,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="5">
         <v>45902</v>
       </c>
@@ -1578,7 +1759,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="5">
         <v>45909</v>
       </c>
@@ -1601,7 +1782,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="5">
         <v>45916</v>
       </c>
@@ -1624,7 +1805,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="5">
         <v>45923</v>
       </c>
@@ -1647,7 +1828,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="5">
         <v>45930</v>
       </c>
@@ -1670,7 +1851,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="5">
         <v>45944</v>
       </c>
@@ -1693,7 +1874,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="5">
         <v>45951</v>
       </c>
@@ -1716,7 +1897,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="5">
         <v>45958</v>
       </c>
@@ -1739,7 +1920,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="5">
         <v>45965</v>
       </c>
@@ -1762,7 +1943,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="5">
         <v>45972</v>
       </c>
@@ -1785,7 +1966,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="5">
         <v>45979</v>
       </c>
@@ -1808,7 +1989,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="5">
         <v>45986</v>
       </c>
@@ -1831,7 +2012,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="5">
         <v>45993</v>
       </c>
@@ -1854,7 +2035,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="5">
         <v>46000</v>
       </c>
@@ -1877,7 +2058,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="5">
         <v>46007</v>
       </c>
@@ -1900,7 +2081,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="5">
         <v>46014</v>
       </c>
@@ -1923,7 +2104,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="5">
         <v>46021</v>
       </c>
@@ -1946,7 +2127,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="5">
         <v>46028</v>
       </c>
@@ -1969,7 +2150,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="8">
         <v>46035</v>
       </c>
@@ -1992,7 +2173,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="8">
         <v>46042</v>
       </c>
@@ -2015,7 +2196,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="8">
         <v>46049</v>
       </c>
@@ -2038,7 +2219,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="8">
         <v>46056</v>
       </c>
@@ -2061,7 +2242,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="8">
         <v>46063</v>
       </c>
@@ -2084,7 +2265,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="8">
         <v>46077</v>
       </c>
@@ -2107,7 +2288,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="8">
         <v>46084</v>
       </c>
@@ -2130,7 +2311,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="8">
         <v>46091</v>
       </c>
@@ -2153,7 +2334,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="8">
         <v>46098</v>
       </c>
@@ -2176,7 +2357,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="8">
         <v>46105</v>
       </c>
@@ -2199,7 +2380,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="8">
         <v>46112</v>
       </c>
@@ -2222,7 +2403,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="8">
         <v>46119</v>
       </c>
@@ -2245,7 +2426,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="8">
         <v>46126</v>
       </c>
@@ -2268,7 +2449,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="8">
         <v>46133</v>
       </c>
@@ -2289,6 +2470,144 @@
       </c>
       <c r="G39" s="11">
         <v>85</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="11">
+        <v>79</v>
+      </c>
+      <c r="F40" s="11">
+        <v>90</v>
+      </c>
+      <c r="G40" s="11">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="11">
+        <v>77</v>
+      </c>
+      <c r="F41" s="11">
+        <v>88</v>
+      </c>
+      <c r="G41" s="11">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="11">
+        <v>75</v>
+      </c>
+      <c r="F42" s="11">
+        <v>86</v>
+      </c>
+      <c r="G42" s="11">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="11">
+        <v>75</v>
+      </c>
+      <c r="F43" s="11">
+        <v>86</v>
+      </c>
+      <c r="G43" s="11">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="11">
+        <v>75</v>
+      </c>
+      <c r="F44" s="11">
+        <v>86</v>
+      </c>
+      <c r="G44" s="11">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="11">
+        <v>75</v>
+      </c>
+      <c r="F45" s="11">
+        <v>86</v>
+      </c>
+      <c r="G45" s="11">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2299,19 +2618,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C33C41F-CAF1-4FD5-8D91-A49D334C85A7}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="11.19921875" style="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9.5546875" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="14" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2334,7 +2653,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="5">
         <v>45860</v>
       </c>
@@ -2357,7 +2676,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="5">
         <v>45867</v>
       </c>
@@ -2380,7 +2699,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="5">
         <v>45874</v>
       </c>
@@ -2403,7 +2722,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="5">
         <v>45881</v>
       </c>
@@ -2426,7 +2745,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="5">
         <v>45888</v>
       </c>
@@ -2449,7 +2768,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="5">
         <v>45895</v>
       </c>
@@ -2472,7 +2791,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="5">
         <v>45902</v>
       </c>
@@ -2495,7 +2814,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="5">
         <v>45909</v>
       </c>
@@ -2518,7 +2837,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="5">
         <v>45916</v>
       </c>
@@ -2541,7 +2860,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="5">
         <v>45923</v>
       </c>
@@ -2564,7 +2883,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="5">
         <v>45930</v>
       </c>
@@ -2587,7 +2906,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="5">
         <v>45944</v>
       </c>
@@ -2610,7 +2929,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="5">
         <v>45951</v>
       </c>
@@ -2633,7 +2952,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="5">
         <v>45958</v>
       </c>
@@ -2656,7 +2975,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="5">
         <v>45965</v>
       </c>
@@ -2679,7 +2998,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="5">
         <v>45972</v>
       </c>
@@ -2702,7 +3021,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="5">
         <v>45979</v>
       </c>
@@ -2725,7 +3044,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="5">
         <v>45986</v>
       </c>
@@ -2748,7 +3067,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="5">
         <v>45993</v>
       </c>
@@ -2771,7 +3090,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="5">
         <v>46000</v>
       </c>
@@ -2794,7 +3113,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="5">
         <v>46007</v>
       </c>
@@ -2817,7 +3136,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="5">
         <v>46014</v>
       </c>
@@ -2840,7 +3159,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="5">
         <v>46021</v>
       </c>
@@ -2863,7 +3182,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="5">
         <v>46028</v>
       </c>
@@ -2886,7 +3205,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="8">
         <v>46035</v>
       </c>
@@ -2909,7 +3228,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="8">
         <v>46042</v>
       </c>
@@ -2932,7 +3251,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="8">
         <v>46049</v>
       </c>
@@ -2955,7 +3274,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="8">
         <v>46056</v>
       </c>
@@ -2978,7 +3297,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="8">
         <v>46063</v>
       </c>
@@ -3001,7 +3320,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="8">
         <v>46077</v>
       </c>
@@ -3024,7 +3343,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="8">
         <v>46084</v>
       </c>
@@ -3047,7 +3366,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="8">
         <v>46091</v>
       </c>
@@ -3070,7 +3389,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="8">
         <v>46098</v>
       </c>
@@ -3093,7 +3412,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="8">
         <v>46105</v>
       </c>
@@ -3116,7 +3435,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="8">
         <v>46112</v>
       </c>
@@ -3139,7 +3458,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="8">
         <v>46119</v>
       </c>
@@ -3162,7 +3481,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="8">
         <v>46126</v>
       </c>
@@ -3185,7 +3504,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="8">
         <v>46133</v>
       </c>
@@ -3206,6 +3525,144 @@
       </c>
       <c r="G39" s="14">
         <v>175</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="14">
+        <v>165</v>
+      </c>
+      <c r="F40" s="14">
+        <v>180</v>
+      </c>
+      <c r="G40" s="14">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="14">
+        <v>160</v>
+      </c>
+      <c r="F41" s="14">
+        <v>175</v>
+      </c>
+      <c r="G41" s="14">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="14">
+        <v>158</v>
+      </c>
+      <c r="F42" s="14">
+        <v>173</v>
+      </c>
+      <c r="G42" s="14">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="14">
+        <v>158</v>
+      </c>
+      <c r="F43" s="14">
+        <v>173</v>
+      </c>
+      <c r="G43" s="14">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="14">
+        <v>158</v>
+      </c>
+      <c r="F44" s="14">
+        <v>173</v>
+      </c>
+      <c r="G44" s="14">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="14">
+        <v>158</v>
+      </c>
+      <c r="F45" s="14">
+        <v>173</v>
+      </c>
+      <c r="G45" s="14">
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -3215,2748 +3672,1320 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A33F9B6-7347-4C68-802E-E71624384C9E}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{804C6E38-9512-4F25-B73E-A84B442434F8}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="11.19921875" style="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="12.6640625" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" style="26"/>
+    <col min="7" max="7" width="11.21875" style="26" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="22" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="5">
-        <v>45860</v>
-      </c>
-      <c r="B2" s="5">
-        <v>45860</v>
-      </c>
-      <c r="C2" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="13">
-        <v>30</v>
-      </c>
-      <c r="F2" s="13">
-        <v>34</v>
-      </c>
-      <c r="G2" s="13">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="5">
-        <v>45867</v>
-      </c>
-      <c r="B3" s="5">
-        <v>45867</v>
-      </c>
-      <c r="C3" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="13">
-        <v>30</v>
-      </c>
-      <c r="F3" s="13">
-        <v>34</v>
-      </c>
-      <c r="G3" s="13">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="5">
-        <v>45874</v>
-      </c>
-      <c r="B4" s="5">
-        <v>45874</v>
-      </c>
-      <c r="C4" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="13">
-        <v>30</v>
-      </c>
-      <c r="F4" s="13">
-        <v>34</v>
-      </c>
-      <c r="G4" s="13">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="5">
-        <v>45881</v>
-      </c>
-      <c r="B5" s="5">
-        <v>45881</v>
-      </c>
-      <c r="C5" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="13">
-        <v>30</v>
-      </c>
-      <c r="F5" s="13">
-        <v>34</v>
-      </c>
-      <c r="G5" s="13">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="5">
-        <v>45888</v>
-      </c>
-      <c r="B6" s="5">
-        <v>45888</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="13">
-        <v>30</v>
-      </c>
-      <c r="F6" s="13">
-        <v>34</v>
-      </c>
-      <c r="G6" s="13">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="5">
-        <v>45895</v>
-      </c>
-      <c r="B7" s="5">
-        <v>45895</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="13">
-        <v>31</v>
-      </c>
-      <c r="F7" s="13">
-        <v>35</v>
-      </c>
-      <c r="G7" s="13">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="5">
-        <v>45902</v>
-      </c>
-      <c r="B8" s="5">
-        <v>45902</v>
-      </c>
-      <c r="C8" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="13">
-        <v>31.4</v>
-      </c>
-      <c r="F8" s="13">
-        <v>35.4</v>
-      </c>
-      <c r="G8" s="13">
-        <v>33.4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="5">
-        <v>45909</v>
-      </c>
-      <c r="B9" s="5">
-        <v>45909</v>
-      </c>
-      <c r="C9" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="13">
-        <v>31.8</v>
-      </c>
-      <c r="F9" s="13">
-        <v>35.799999999999997</v>
-      </c>
-      <c r="G9" s="13">
-        <v>33.799999999999997</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="5">
-        <v>45916</v>
-      </c>
-      <c r="B10" s="5">
-        <v>45916</v>
-      </c>
-      <c r="C10" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="13">
-        <v>32</v>
-      </c>
-      <c r="F10" s="13">
-        <v>36</v>
-      </c>
-      <c r="G10" s="13">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="5">
-        <v>45923</v>
-      </c>
-      <c r="B11" s="5">
-        <v>45923</v>
-      </c>
-      <c r="C11" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="13">
-        <v>32</v>
-      </c>
-      <c r="F11" s="13">
-        <v>36</v>
-      </c>
-      <c r="G11" s="13">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="5">
-        <v>45930</v>
-      </c>
-      <c r="B12" s="5">
-        <v>45930</v>
-      </c>
-      <c r="C12" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="13">
-        <v>32</v>
-      </c>
-      <c r="F12" s="13">
-        <v>36</v>
-      </c>
-      <c r="G12" s="13">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="5">
-        <v>45944</v>
-      </c>
-      <c r="B13" s="5">
-        <v>45944</v>
-      </c>
-      <c r="C13" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="13">
-        <v>38.6</v>
-      </c>
-      <c r="F13" s="13">
-        <v>42.6</v>
-      </c>
-      <c r="G13" s="13">
-        <v>40.6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="5">
-        <v>45951</v>
-      </c>
-      <c r="B14" s="5">
-        <v>45951</v>
-      </c>
-      <c r="C14" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="13">
-        <v>38.6</v>
-      </c>
-      <c r="F14" s="13">
-        <v>42.6</v>
-      </c>
-      <c r="G14" s="13">
-        <v>40.6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="5">
-        <v>45958</v>
-      </c>
-      <c r="B15" s="5">
-        <v>45958</v>
-      </c>
-      <c r="C15" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="13">
-        <v>38.6</v>
-      </c>
-      <c r="F15" s="13">
-        <v>42.6</v>
-      </c>
-      <c r="G15" s="13">
-        <v>40.6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="5">
-        <v>45965</v>
-      </c>
-      <c r="B16" s="5">
-        <v>45965</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" s="13">
-        <v>38.6</v>
-      </c>
-      <c r="F16" s="13">
-        <v>42.6</v>
-      </c>
-      <c r="G16" s="13">
-        <v>40.6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="5">
-        <v>45972</v>
-      </c>
-      <c r="B17" s="5">
-        <v>45972</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" s="13">
-        <v>38.6</v>
-      </c>
-      <c r="F17" s="13">
-        <v>42.6</v>
-      </c>
-      <c r="G17" s="13">
-        <v>40.6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="5">
-        <v>45979</v>
-      </c>
-      <c r="B18" s="5">
-        <v>45979</v>
-      </c>
-      <c r="C18" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" s="13">
-        <v>38.6</v>
-      </c>
-      <c r="F18" s="13">
-        <v>42.6</v>
-      </c>
-      <c r="G18" s="13">
-        <v>40.6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="5">
-        <v>45986</v>
-      </c>
-      <c r="B19" s="5">
-        <v>45986</v>
-      </c>
-      <c r="C19" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="13">
-        <v>58</v>
-      </c>
-      <c r="F19" s="13">
-        <v>62</v>
-      </c>
-      <c r="G19" s="13">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="5">
-        <v>45993</v>
-      </c>
-      <c r="B20" s="5">
-        <v>45993</v>
-      </c>
-      <c r="C20" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="13">
-        <v>83</v>
-      </c>
-      <c r="F20" s="13">
+    <row r="2" spans="1:7">
+      <c r="A2" s="23">
+        <v>46161</v>
+      </c>
+      <c r="B2" s="23">
+        <v>46161</v>
+      </c>
+      <c r="C2" s="24">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="26">
+        <v>70</v>
+      </c>
+      <c r="F2" s="26">
+        <v>85</v>
+      </c>
+      <c r="G2" s="26">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="23">
+        <v>46168</v>
+      </c>
+      <c r="B3" s="23">
+        <v>46168</v>
+      </c>
+      <c r="C3" s="24">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="26">
+        <v>70</v>
+      </c>
+      <c r="F3" s="26">
+        <v>85</v>
+      </c>
+      <c r="G3" s="26">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="23">
+        <v>46175</v>
+      </c>
+      <c r="B4" s="23">
+        <v>46175</v>
+      </c>
+      <c r="C4" s="24">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="26">
+        <v>70</v>
+      </c>
+      <c r="F4" s="26">
+        <v>85</v>
+      </c>
+      <c r="G4" s="26">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="23">
+        <v>46182</v>
+      </c>
+      <c r="B5" s="23">
+        <v>46182</v>
+      </c>
+      <c r="C5" s="24">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="26">
+        <v>72</v>
+      </c>
+      <c r="F5" s="26">
         <v>87</v>
       </c>
-      <c r="G20" s="13">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="5">
-        <v>46000</v>
-      </c>
-      <c r="B21" s="5">
-        <v>46000</v>
-      </c>
-      <c r="C21" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E21" s="13">
-        <v>108</v>
-      </c>
-      <c r="F21" s="13">
-        <v>112</v>
-      </c>
-      <c r="G21" s="13">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="5">
-        <v>46007</v>
-      </c>
-      <c r="B22" s="5">
-        <v>46007</v>
-      </c>
-      <c r="C22" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22" s="13">
-        <v>108</v>
-      </c>
-      <c r="F22" s="13">
-        <v>112</v>
-      </c>
-      <c r="G22" s="13">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="5">
-        <v>46014</v>
-      </c>
-      <c r="B23" s="5">
-        <v>46014</v>
-      </c>
-      <c r="C23" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" s="13">
-        <v>108</v>
-      </c>
-      <c r="F23" s="13">
-        <v>112</v>
-      </c>
-      <c r="G23" s="13">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="5">
-        <v>46021</v>
-      </c>
-      <c r="B24" s="5">
-        <v>46021</v>
-      </c>
-      <c r="C24" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E24" s="13">
-        <v>108</v>
-      </c>
-      <c r="F24" s="13">
-        <v>112</v>
-      </c>
-      <c r="G24" s="13">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="5">
-        <v>46028</v>
-      </c>
-      <c r="B25" s="5">
-        <v>46028</v>
-      </c>
-      <c r="C25" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" s="13">
-        <v>123</v>
-      </c>
-      <c r="F25" s="13">
-        <v>127</v>
-      </c>
-      <c r="G25" s="13">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="8">
-        <v>46035</v>
-      </c>
-      <c r="B26" s="8">
-        <v>46035</v>
-      </c>
-      <c r="C26" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E26" s="13">
-        <v>123</v>
-      </c>
-      <c r="F26" s="13">
-        <v>127</v>
-      </c>
-      <c r="G26" s="13">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="8">
-        <v>46042</v>
-      </c>
-      <c r="B27" s="8">
-        <v>46042</v>
-      </c>
-      <c r="C27" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E27" s="13">
-        <v>158</v>
-      </c>
-      <c r="F27" s="13">
-        <v>162</v>
-      </c>
-      <c r="G27" s="13">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="8">
-        <v>46049</v>
-      </c>
-      <c r="B28" s="8">
-        <v>46049</v>
-      </c>
-      <c r="C28" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="14">
-        <v>168</v>
-      </c>
-      <c r="F28" s="14">
-        <v>172</v>
-      </c>
-      <c r="G28" s="14">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="8">
-        <v>46056</v>
-      </c>
-      <c r="B29" s="8">
-        <v>46056</v>
-      </c>
-      <c r="C29" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="14">
-        <v>168</v>
-      </c>
-      <c r="F29" s="14">
-        <v>172</v>
-      </c>
-      <c r="G29" s="14">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="8">
-        <v>46063</v>
-      </c>
-      <c r="B30" s="8">
-        <v>46063</v>
-      </c>
-      <c r="C30" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="14">
-        <v>168</v>
-      </c>
-      <c r="F30" s="14">
-        <v>172</v>
-      </c>
-      <c r="G30" s="14">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="8">
-        <v>46077</v>
-      </c>
-      <c r="B31" s="8">
-        <v>46077</v>
-      </c>
-      <c r="C31" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="14">
-        <v>168</v>
-      </c>
-      <c r="F31" s="14">
-        <v>172</v>
-      </c>
-      <c r="G31" s="14">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" s="8">
-        <v>46084</v>
-      </c>
-      <c r="B32" s="8">
-        <v>46084</v>
-      </c>
-      <c r="C32" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="14">
-        <v>168</v>
-      </c>
-      <c r="F32" s="14">
-        <v>172</v>
-      </c>
-      <c r="G32" s="14">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" s="8">
-        <v>46091</v>
-      </c>
-      <c r="B33" s="8">
-        <v>46091</v>
-      </c>
-      <c r="C33" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="14">
-        <v>188</v>
-      </c>
-      <c r="F33" s="14">
-        <v>192</v>
-      </c>
-      <c r="G33" s="14">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A34" s="8">
-        <v>46098</v>
-      </c>
-      <c r="B34" s="8">
-        <v>46098</v>
-      </c>
-      <c r="C34" s="6">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" s="14">
-        <v>188</v>
-      </c>
-      <c r="F34" s="14">
-        <v>192</v>
-      </c>
-      <c r="G34" s="14">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A35" s="8">
-        <v>46105</v>
-      </c>
-      <c r="B35" s="8">
-        <v>46105</v>
-      </c>
-      <c r="C35" s="6">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E35" s="14">
-        <v>188</v>
-      </c>
-      <c r="F35" s="14">
-        <v>192</v>
-      </c>
-      <c r="G35" s="14">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" s="8">
-        <v>46112</v>
-      </c>
-      <c r="B36" s="8">
-        <v>46112</v>
-      </c>
-      <c r="C36" s="6">
-        <v>0.45833333333333198</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E36" s="14">
-        <v>168</v>
-      </c>
-      <c r="F36" s="14">
-        <v>172</v>
-      </c>
-      <c r="G36" s="14">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A37" s="8">
-        <v>46119</v>
-      </c>
-      <c r="B37" s="8">
-        <v>46119</v>
-      </c>
-      <c r="C37" s="6">
-        <v>0.45833333333333198</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E37" s="14">
-        <v>168</v>
-      </c>
-      <c r="F37" s="14">
-        <v>172</v>
-      </c>
-      <c r="G37" s="14">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38" s="8">
-        <v>46126</v>
-      </c>
-      <c r="B38" s="8">
-        <v>46126</v>
-      </c>
-      <c r="C38" s="6">
-        <v>0.45833333333333198</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E38" s="14">
-        <v>163</v>
-      </c>
-      <c r="F38" s="14">
-        <v>167</v>
-      </c>
-      <c r="G38" s="14">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A39" s="8">
-        <v>46133</v>
-      </c>
-      <c r="B39" s="8">
-        <v>46133</v>
-      </c>
-      <c r="C39" s="6">
-        <v>0.45833333333333098</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E39" s="14">
-        <v>158</v>
-      </c>
-      <c r="F39" s="14">
-        <v>162</v>
-      </c>
-      <c r="G39" s="14">
-        <v>160</v>
+      <c r="G5" s="26">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55494817-78A6-45DF-9F77-86066DAB20E2}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04103911-DA80-4A49-87A1-FE7A2CF5D7A5}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="17"/>
-    <col min="7" max="7" width="11.19921875" style="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="12.6640625" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.88671875" style="26"/>
+    <col min="7" max="7" width="11.21875" style="26" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="22" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="5">
-        <v>45860</v>
-      </c>
-      <c r="B2" s="5">
-        <v>45860</v>
-      </c>
-      <c r="C2" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="16">
-        <v>33</v>
-      </c>
-      <c r="F2" s="16">
-        <v>37</v>
-      </c>
-      <c r="G2" s="16">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="5">
-        <v>45867</v>
-      </c>
-      <c r="B3" s="5">
-        <v>45867</v>
-      </c>
-      <c r="C3" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="16">
-        <v>33</v>
-      </c>
-      <c r="F3" s="16">
-        <v>37</v>
-      </c>
-      <c r="G3" s="16">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="5">
-        <v>45874</v>
-      </c>
-      <c r="B4" s="5">
-        <v>45874</v>
-      </c>
-      <c r="C4" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="16">
-        <v>33</v>
-      </c>
-      <c r="F4" s="16">
-        <v>37</v>
-      </c>
-      <c r="G4" s="16">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="5">
-        <v>45881</v>
-      </c>
-      <c r="B5" s="5">
-        <v>45881</v>
-      </c>
-      <c r="C5" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="16">
-        <v>33</v>
-      </c>
-      <c r="F5" s="16">
-        <v>37</v>
-      </c>
-      <c r="G5" s="16">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="5">
-        <v>45888</v>
-      </c>
-      <c r="B6" s="5">
-        <v>45888</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="16">
-        <v>33</v>
-      </c>
-      <c r="F6" s="16">
-        <v>37</v>
-      </c>
-      <c r="G6" s="16">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="5">
-        <v>45895</v>
-      </c>
-      <c r="B7" s="5">
-        <v>45895</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="16">
-        <v>34</v>
-      </c>
-      <c r="F7" s="16">
-        <v>38</v>
-      </c>
-      <c r="G7" s="16">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="5">
-        <v>45902</v>
-      </c>
-      <c r="B8" s="5">
-        <v>45902</v>
-      </c>
-      <c r="C8" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="16">
-        <v>35</v>
-      </c>
-      <c r="F8" s="16">
-        <v>39</v>
-      </c>
-      <c r="G8" s="16">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="5">
-        <v>45909</v>
-      </c>
-      <c r="B9" s="5">
-        <v>45909</v>
-      </c>
-      <c r="C9" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="16">
-        <v>35.4</v>
-      </c>
-      <c r="F9" s="16">
-        <v>39.4</v>
-      </c>
-      <c r="G9" s="16">
-        <v>37.4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="5">
-        <v>45916</v>
-      </c>
-      <c r="B10" s="5">
-        <v>45916</v>
-      </c>
-      <c r="C10" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="16">
-        <v>36</v>
-      </c>
-      <c r="F10" s="16">
-        <v>40</v>
-      </c>
-      <c r="G10" s="16">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="5">
-        <v>45923</v>
-      </c>
-      <c r="B11" s="5">
-        <v>45923</v>
-      </c>
-      <c r="C11" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="16">
-        <v>36</v>
-      </c>
-      <c r="F11" s="16">
-        <v>40</v>
-      </c>
-      <c r="G11" s="16">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="5">
-        <v>45930</v>
-      </c>
-      <c r="B12" s="5">
-        <v>45930</v>
-      </c>
-      <c r="C12" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="16">
-        <v>36</v>
-      </c>
-      <c r="F12" s="16">
-        <v>40</v>
-      </c>
-      <c r="G12" s="16">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="5">
-        <v>45944</v>
-      </c>
-      <c r="B13" s="5">
-        <v>45944</v>
-      </c>
-      <c r="C13" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="16">
-        <v>43</v>
-      </c>
-      <c r="F13" s="16">
-        <v>47</v>
-      </c>
-      <c r="G13" s="16">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="5">
-        <v>45951</v>
-      </c>
-      <c r="B14" s="5">
-        <v>45951</v>
-      </c>
-      <c r="C14" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="16">
-        <v>43</v>
-      </c>
-      <c r="F14" s="16">
-        <v>47</v>
-      </c>
-      <c r="G14" s="16">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="5">
-        <v>45958</v>
-      </c>
-      <c r="B15" s="5">
-        <v>45958</v>
-      </c>
-      <c r="C15" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="16">
-        <v>43</v>
-      </c>
-      <c r="F15" s="16">
-        <v>47</v>
-      </c>
-      <c r="G15" s="16">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="5">
-        <v>45965</v>
-      </c>
-      <c r="B16" s="5">
-        <v>45965</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" s="16">
-        <v>43</v>
-      </c>
-      <c r="F16" s="16">
-        <v>47</v>
-      </c>
-      <c r="G16" s="16">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="5">
-        <v>45972</v>
-      </c>
-      <c r="B17" s="5">
-        <v>45972</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" s="16">
-        <v>43</v>
-      </c>
-      <c r="F17" s="16">
-        <v>47</v>
-      </c>
-      <c r="G17" s="16">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="5">
-        <v>45979</v>
-      </c>
-      <c r="B18" s="5">
-        <v>45979</v>
-      </c>
-      <c r="C18" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" s="16">
-        <v>43</v>
-      </c>
-      <c r="F18" s="16">
-        <v>47</v>
-      </c>
-      <c r="G18" s="16">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="5">
-        <v>45986</v>
-      </c>
-      <c r="B19" s="5">
-        <v>45986</v>
-      </c>
-      <c r="C19" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="16">
-        <v>63</v>
-      </c>
-      <c r="F19" s="16">
-        <v>67</v>
-      </c>
-      <c r="G19" s="16">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="5">
-        <v>45993</v>
-      </c>
-      <c r="B20" s="5">
-        <v>45993</v>
-      </c>
-      <c r="C20" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="16">
-        <v>88</v>
-      </c>
-      <c r="F20" s="16">
+    <row r="2" spans="1:7">
+      <c r="A2" s="23">
+        <v>46161</v>
+      </c>
+      <c r="B2" s="23">
+        <v>46161</v>
+      </c>
+      <c r="C2" s="24">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="26">
+        <v>75</v>
+      </c>
+      <c r="F2" s="26">
+        <v>90</v>
+      </c>
+      <c r="G2" s="26">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="23">
+        <v>46168</v>
+      </c>
+      <c r="B3" s="23">
+        <v>46168</v>
+      </c>
+      <c r="C3" s="24">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="26">
+        <v>75</v>
+      </c>
+      <c r="F3" s="26">
+        <v>90</v>
+      </c>
+      <c r="G3" s="26">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="23">
+        <v>46175</v>
+      </c>
+      <c r="B4" s="23">
+        <v>46175</v>
+      </c>
+      <c r="C4" s="24">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="26">
+        <v>75</v>
+      </c>
+      <c r="F4" s="26">
+        <v>90</v>
+      </c>
+      <c r="G4" s="26">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="23">
+        <v>46182</v>
+      </c>
+      <c r="B5" s="23">
+        <v>46182</v>
+      </c>
+      <c r="C5" s="24">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="26">
+        <v>77</v>
+      </c>
+      <c r="F5" s="26">
         <v>92</v>
       </c>
-      <c r="G20" s="16">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="5">
-        <v>46000</v>
-      </c>
-      <c r="B21" s="5">
-        <v>46000</v>
-      </c>
-      <c r="C21" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E21" s="16">
-        <v>118</v>
-      </c>
-      <c r="F21" s="16">
-        <v>122</v>
-      </c>
-      <c r="G21" s="16">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="5">
-        <v>46007</v>
-      </c>
-      <c r="B22" s="5">
-        <v>46007</v>
-      </c>
-      <c r="C22" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22" s="16">
-        <v>118</v>
-      </c>
-      <c r="F22" s="16">
-        <v>122</v>
-      </c>
-      <c r="G22" s="16">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="5">
-        <v>46014</v>
-      </c>
-      <c r="B23" s="5">
-        <v>46014</v>
-      </c>
-      <c r="C23" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" s="16">
-        <v>118</v>
-      </c>
-      <c r="F23" s="16">
-        <v>122</v>
-      </c>
-      <c r="G23" s="16">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="5">
-        <v>46021</v>
-      </c>
-      <c r="B24" s="5">
-        <v>46021</v>
-      </c>
-      <c r="C24" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E24" s="16">
-        <v>118</v>
-      </c>
-      <c r="F24" s="16">
-        <v>122</v>
-      </c>
-      <c r="G24" s="16">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="5">
-        <v>46028</v>
-      </c>
-      <c r="B25" s="5">
-        <v>46028</v>
-      </c>
-      <c r="C25" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" s="16">
-        <v>143</v>
-      </c>
-      <c r="F25" s="16">
-        <v>147</v>
-      </c>
-      <c r="G25" s="16">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="8">
-        <v>46035</v>
-      </c>
-      <c r="B26" s="8">
-        <v>46035</v>
-      </c>
-      <c r="C26" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E26" s="16">
-        <v>143</v>
-      </c>
-      <c r="F26" s="16">
-        <v>147</v>
-      </c>
-      <c r="G26" s="16">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="8">
-        <v>46042</v>
-      </c>
-      <c r="B27" s="8">
-        <v>46042</v>
-      </c>
-      <c r="C27" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E27" s="16">
-        <v>167</v>
-      </c>
-      <c r="F27" s="16">
-        <v>172</v>
-      </c>
-      <c r="G27" s="16">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="8">
-        <v>46049</v>
-      </c>
-      <c r="B28" s="8">
-        <v>46049</v>
-      </c>
-      <c r="C28" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="17">
-        <v>177</v>
-      </c>
-      <c r="F28" s="17">
-        <v>182</v>
-      </c>
-      <c r="G28" s="17">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="8">
-        <v>46056</v>
-      </c>
-      <c r="B29" s="8">
-        <v>46056</v>
-      </c>
-      <c r="C29" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="17">
-        <v>177</v>
-      </c>
-      <c r="F29" s="17">
-        <v>182</v>
-      </c>
-      <c r="G29" s="17">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="8">
-        <v>46063</v>
-      </c>
-      <c r="B30" s="8">
-        <v>46063</v>
-      </c>
-      <c r="C30" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="17">
-        <v>177</v>
-      </c>
-      <c r="F30" s="17">
-        <v>182</v>
-      </c>
-      <c r="G30" s="17">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="8">
-        <v>46077</v>
-      </c>
-      <c r="B31" s="8">
-        <v>46077</v>
-      </c>
-      <c r="C31" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="17">
-        <v>177</v>
-      </c>
-      <c r="F31" s="17">
-        <v>182</v>
-      </c>
-      <c r="G31" s="17">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" s="8">
-        <v>46084</v>
-      </c>
-      <c r="B32" s="8">
-        <v>46084</v>
-      </c>
-      <c r="C32" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="17">
-        <v>177</v>
-      </c>
-      <c r="F32" s="17">
-        <v>182</v>
-      </c>
-      <c r="G32" s="17">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" s="8">
-        <v>46091</v>
-      </c>
-      <c r="B33" s="8">
-        <v>46091</v>
-      </c>
-      <c r="C33" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="17">
-        <v>197</v>
-      </c>
-      <c r="F33" s="17">
-        <v>202</v>
-      </c>
-      <c r="G33" s="17">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A34" s="8">
-        <v>46098</v>
-      </c>
-      <c r="B34" s="8">
-        <v>46098</v>
-      </c>
-      <c r="C34" s="6">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" s="17">
-        <v>197</v>
-      </c>
-      <c r="F34" s="17">
-        <v>202</v>
-      </c>
-      <c r="G34" s="17">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A35" s="8">
-        <v>46105</v>
-      </c>
-      <c r="B35" s="8">
-        <v>46105</v>
-      </c>
-      <c r="C35" s="6">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E35" s="17">
-        <v>197</v>
-      </c>
-      <c r="F35" s="17">
-        <v>202</v>
-      </c>
-      <c r="G35" s="17">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" s="8">
-        <v>46112</v>
-      </c>
-      <c r="B36" s="8">
-        <v>46112</v>
-      </c>
-      <c r="C36" s="6">
-        <v>0.45833333333333198</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E36" s="17">
-        <v>177</v>
-      </c>
-      <c r="F36" s="17">
-        <v>182</v>
-      </c>
-      <c r="G36" s="17">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A37" s="8">
-        <v>46119</v>
-      </c>
-      <c r="B37" s="8">
-        <v>46119</v>
-      </c>
-      <c r="C37" s="6">
-        <v>0.45833333333333198</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E37" s="17">
-        <v>177</v>
-      </c>
-      <c r="F37" s="17">
-        <v>182</v>
-      </c>
-      <c r="G37" s="17">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38" s="8">
-        <v>46126</v>
-      </c>
-      <c r="B38" s="8">
-        <v>46126</v>
-      </c>
-      <c r="C38" s="6">
-        <v>0.45833333333333198</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E38" s="17">
-        <v>167</v>
-      </c>
-      <c r="F38" s="17">
-        <v>172</v>
-      </c>
-      <c r="G38" s="17">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A39" s="8">
-        <v>46133</v>
-      </c>
-      <c r="B39" s="8">
-        <v>46133</v>
-      </c>
-      <c r="C39" s="6">
-        <v>0.45833333333333098</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E39" s="17">
-        <v>164</v>
-      </c>
-      <c r="F39" s="17">
-        <v>169</v>
-      </c>
-      <c r="G39" s="17">
-        <v>167</v>
+      <c r="G5" s="26">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B6A378-E9BB-4F97-B1F3-B76BB8A3CEFF}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A33F9B6-7347-4C68-802E-E71624384C9E}">
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="11.19921875" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="12.6640625" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" style="30"/>
+    <col min="7" max="7" width="11.21875" style="30" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="27" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="5">
+    <row r="2" spans="1:7">
+      <c r="A2" s="28">
         <v>45860</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="28">
         <v>45860</v>
       </c>
-      <c r="C2" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="C2" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="29">
+        <v>30</v>
+      </c>
+      <c r="F2" s="29">
+        <v>34</v>
+      </c>
+      <c r="G2" s="29">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="28">
+        <v>45867</v>
+      </c>
+      <c r="B3" s="28">
+        <v>45867</v>
+      </c>
+      <c r="C3" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="29">
+        <v>30</v>
+      </c>
+      <c r="F3" s="29">
+        <v>34</v>
+      </c>
+      <c r="G3" s="29">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="28">
+        <v>45874</v>
+      </c>
+      <c r="B4" s="28">
+        <v>45874</v>
+      </c>
+      <c r="C4" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="29">
+        <v>30</v>
+      </c>
+      <c r="F4" s="29">
+        <v>34</v>
+      </c>
+      <c r="G4" s="29">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="28">
+        <v>45881</v>
+      </c>
+      <c r="B5" s="28">
+        <v>45881</v>
+      </c>
+      <c r="C5" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="29">
+        <v>30</v>
+      </c>
+      <c r="F5" s="29">
+        <v>34</v>
+      </c>
+      <c r="G5" s="29">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="28">
+        <v>45888</v>
+      </c>
+      <c r="B6" s="28">
+        <v>45888</v>
+      </c>
+      <c r="C6" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="29">
+        <v>30</v>
+      </c>
+      <c r="F6" s="29">
+        <v>34</v>
+      </c>
+      <c r="G6" s="29">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="28">
+        <v>45895</v>
+      </c>
+      <c r="B7" s="28">
+        <v>45895</v>
+      </c>
+      <c r="C7" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="29">
+        <v>31</v>
+      </c>
+      <c r="F7" s="29">
+        <v>35</v>
+      </c>
+      <c r="G7" s="29">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="28">
+        <v>45902</v>
+      </c>
+      <c r="B8" s="28">
+        <v>45902</v>
+      </c>
+      <c r="C8" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="29">
+        <v>31.4</v>
+      </c>
+      <c r="F8" s="29">
+        <v>35.4</v>
+      </c>
+      <c r="G8" s="29">
+        <v>33.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="28">
+        <v>45909</v>
+      </c>
+      <c r="B9" s="28">
+        <v>45909</v>
+      </c>
+      <c r="C9" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="29">
+        <v>31.8</v>
+      </c>
+      <c r="F9" s="29">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="G9" s="29">
+        <v>33.799999999999997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="28">
+        <v>45916</v>
+      </c>
+      <c r="B10" s="28">
+        <v>45916</v>
+      </c>
+      <c r="C10" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="29">
+        <v>32</v>
+      </c>
+      <c r="F10" s="29">
+        <v>36</v>
+      </c>
+      <c r="G10" s="29">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="28">
+        <v>45923</v>
+      </c>
+      <c r="B11" s="28">
+        <v>45923</v>
+      </c>
+      <c r="C11" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="29">
+        <v>32</v>
+      </c>
+      <c r="F11" s="29">
+        <v>36</v>
+      </c>
+      <c r="G11" s="29">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="28">
+        <v>45930</v>
+      </c>
+      <c r="B12" s="28">
+        <v>45930</v>
+      </c>
+      <c r="C12" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="29">
+        <v>32</v>
+      </c>
+      <c r="F12" s="29">
+        <v>36</v>
+      </c>
+      <c r="G12" s="29">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="28">
+        <v>45944</v>
+      </c>
+      <c r="B13" s="28">
+        <v>45944</v>
+      </c>
+      <c r="C13" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="29">
+        <v>38.6</v>
+      </c>
+      <c r="F13" s="29">
+        <v>42.6</v>
+      </c>
+      <c r="G13" s="29">
+        <v>40.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="28">
+        <v>45951</v>
+      </c>
+      <c r="B14" s="28">
+        <v>45951</v>
+      </c>
+      <c r="C14" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="29">
+        <v>38.6</v>
+      </c>
+      <c r="F14" s="29">
+        <v>42.6</v>
+      </c>
+      <c r="G14" s="29">
+        <v>40.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="28">
+        <v>45958</v>
+      </c>
+      <c r="B15" s="28">
+        <v>45958</v>
+      </c>
+      <c r="C15" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="29">
+        <v>38.6</v>
+      </c>
+      <c r="F15" s="29">
+        <v>42.6</v>
+      </c>
+      <c r="G15" s="29">
+        <v>40.6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="28">
+        <v>45965</v>
+      </c>
+      <c r="B16" s="28">
+        <v>45965</v>
+      </c>
+      <c r="C16" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="29">
+        <v>38.6</v>
+      </c>
+      <c r="F16" s="29">
+        <v>42.6</v>
+      </c>
+      <c r="G16" s="29">
+        <v>40.6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="28">
+        <v>45972</v>
+      </c>
+      <c r="B17" s="28">
+        <v>45972</v>
+      </c>
+      <c r="C17" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="29">
+        <v>38.6</v>
+      </c>
+      <c r="F17" s="29">
+        <v>42.6</v>
+      </c>
+      <c r="G17" s="29">
+        <v>40.6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="28">
+        <v>45979</v>
+      </c>
+      <c r="B18" s="28">
+        <v>45979</v>
+      </c>
+      <c r="C18" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="29">
+        <v>38.6</v>
+      </c>
+      <c r="F18" s="29">
+        <v>42.6</v>
+      </c>
+      <c r="G18" s="29">
+        <v>40.6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="28">
+        <v>45986</v>
+      </c>
+      <c r="B19" s="28">
+        <v>45986</v>
+      </c>
+      <c r="C19" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="29">
+        <v>58</v>
+      </c>
+      <c r="F19" s="29">
         <v>62</v>
       </c>
-      <c r="F2" s="10">
-        <v>68</v>
-      </c>
-      <c r="G2" s="10">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="5">
-        <v>45867</v>
-      </c>
-      <c r="B3" s="5">
-        <v>45867</v>
-      </c>
-      <c r="C3" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="10">
-        <v>62</v>
-      </c>
-      <c r="F3" s="10">
-        <v>68</v>
-      </c>
-      <c r="G3" s="10">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="5">
-        <v>45874</v>
-      </c>
-      <c r="B4" s="5">
-        <v>45874</v>
-      </c>
-      <c r="C4" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="10">
-        <v>62</v>
-      </c>
-      <c r="F4" s="10">
-        <v>68</v>
-      </c>
-      <c r="G4" s="10">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="5">
-        <v>45881</v>
-      </c>
-      <c r="B5" s="5">
-        <v>45881</v>
-      </c>
-      <c r="C5" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="10">
-        <v>62</v>
-      </c>
-      <c r="F5" s="10">
-        <v>68</v>
-      </c>
-      <c r="G5" s="10">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="5">
-        <v>45888</v>
-      </c>
-      <c r="B6" s="5">
-        <v>45888</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="10">
-        <v>62</v>
-      </c>
-      <c r="F6" s="10">
-        <v>68</v>
-      </c>
-      <c r="G6" s="10">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="5">
-        <v>45895</v>
-      </c>
-      <c r="B7" s="5">
-        <v>45895</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="10">
-        <v>63</v>
-      </c>
-      <c r="F7" s="10">
-        <v>69</v>
-      </c>
-      <c r="G7" s="10">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="5">
-        <v>45902</v>
-      </c>
-      <c r="B8" s="5">
-        <v>45902</v>
-      </c>
-      <c r="C8" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="10">
-        <v>65</v>
-      </c>
-      <c r="F8" s="10">
-        <v>71</v>
-      </c>
-      <c r="G8" s="10">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="5">
-        <v>45909</v>
-      </c>
-      <c r="B9" s="5">
-        <v>45909</v>
-      </c>
-      <c r="C9" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="10">
-        <v>65.5</v>
-      </c>
-      <c r="F9" s="10">
-        <v>71.5</v>
-      </c>
-      <c r="G9" s="10">
-        <v>68.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="5">
-        <v>45916</v>
-      </c>
-      <c r="B10" s="5">
-        <v>45916</v>
-      </c>
-      <c r="C10" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="10">
-        <v>66.2</v>
-      </c>
-      <c r="F10" s="10">
-        <v>72.2</v>
-      </c>
-      <c r="G10" s="10">
-        <v>69.2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="5">
-        <v>45923</v>
-      </c>
-      <c r="B11" s="5">
-        <v>45923</v>
-      </c>
-      <c r="C11" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="10">
-        <v>66.2</v>
-      </c>
-      <c r="F11" s="10">
-        <v>72.2</v>
-      </c>
-      <c r="G11" s="10">
-        <v>69.2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="5">
-        <v>45930</v>
-      </c>
-      <c r="B12" s="5">
-        <v>45930</v>
-      </c>
-      <c r="C12" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="10">
-        <v>66.2</v>
-      </c>
-      <c r="F12" s="10">
-        <v>72.2</v>
-      </c>
-      <c r="G12" s="10">
-        <v>69.2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="5">
-        <v>45944</v>
-      </c>
-      <c r="B13" s="5">
-        <v>45944</v>
-      </c>
-      <c r="C13" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="10">
-        <v>79</v>
-      </c>
-      <c r="F13" s="10">
+      <c r="G19" s="29">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="28">
+        <v>45993</v>
+      </c>
+      <c r="B20" s="28">
+        <v>45993</v>
+      </c>
+      <c r="C20" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="29">
+        <v>83</v>
+      </c>
+      <c r="F20" s="29">
+        <v>87</v>
+      </c>
+      <c r="G20" s="29">
         <v>85</v>
       </c>
-      <c r="G13" s="10">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="5">
-        <v>45951</v>
-      </c>
-      <c r="B14" s="5">
-        <v>45951</v>
-      </c>
-      <c r="C14" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="10">
-        <v>79</v>
-      </c>
-      <c r="F14" s="10">
-        <v>85</v>
-      </c>
-      <c r="G14" s="10">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="5">
-        <v>45958</v>
-      </c>
-      <c r="B15" s="5">
-        <v>45958</v>
-      </c>
-      <c r="C15" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="10">
-        <v>79</v>
-      </c>
-      <c r="F15" s="10">
-        <v>85</v>
-      </c>
-      <c r="G15" s="10">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="5">
-        <v>45965</v>
-      </c>
-      <c r="B16" s="5">
-        <v>45965</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" s="10">
-        <v>79</v>
-      </c>
-      <c r="F16" s="10">
-        <v>85</v>
-      </c>
-      <c r="G16" s="10">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="5">
-        <v>45972</v>
-      </c>
-      <c r="B17" s="5">
-        <v>45972</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" s="10">
-        <v>79</v>
-      </c>
-      <c r="F17" s="10">
-        <v>85</v>
-      </c>
-      <c r="G17" s="10">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="5">
-        <v>45979</v>
-      </c>
-      <c r="B18" s="5">
-        <v>45979</v>
-      </c>
-      <c r="C18" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" s="10">
-        <v>79</v>
-      </c>
-      <c r="F18" s="10">
-        <v>85</v>
-      </c>
-      <c r="G18" s="10">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="5">
-        <v>45986</v>
-      </c>
-      <c r="B19" s="5">
-        <v>45986</v>
-      </c>
-      <c r="C19" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="10">
-        <v>114</v>
-      </c>
-      <c r="F19" s="10">
-        <v>120</v>
-      </c>
-      <c r="G19" s="10">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="5">
-        <v>45993</v>
-      </c>
-      <c r="B20" s="5">
-        <v>45993</v>
-      </c>
-      <c r="C20" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="10">
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="28">
+        <v>46000</v>
+      </c>
+      <c r="B21" s="28">
+        <v>46000</v>
+      </c>
+      <c r="C21" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="29">
+        <v>108</v>
+      </c>
+      <c r="F21" s="29">
+        <v>112</v>
+      </c>
+      <c r="G21" s="29">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="28">
+        <v>46007</v>
+      </c>
+      <c r="B22" s="28">
+        <v>46007</v>
+      </c>
+      <c r="C22" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="29">
+        <v>108</v>
+      </c>
+      <c r="F22" s="29">
+        <v>112</v>
+      </c>
+      <c r="G22" s="29">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="28">
+        <v>46014</v>
+      </c>
+      <c r="B23" s="28">
+        <v>46014</v>
+      </c>
+      <c r="C23" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D23" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="29">
+        <v>108</v>
+      </c>
+      <c r="F23" s="29">
+        <v>112</v>
+      </c>
+      <c r="G23" s="29">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="28">
+        <v>46021</v>
+      </c>
+      <c r="B24" s="28">
+        <v>46021</v>
+      </c>
+      <c r="C24" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="29">
+        <v>108</v>
+      </c>
+      <c r="F24" s="29">
+        <v>112</v>
+      </c>
+      <c r="G24" s="29">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="28">
+        <v>46028</v>
+      </c>
+      <c r="B25" s="28">
+        <v>46028</v>
+      </c>
+      <c r="C25" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D25" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="29">
+        <v>123</v>
+      </c>
+      <c r="F25" s="29">
+        <v>127</v>
+      </c>
+      <c r="G25" s="29">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="23">
+        <v>46035</v>
+      </c>
+      <c r="B26" s="23">
+        <v>46035</v>
+      </c>
+      <c r="C26" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D26" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="29">
+        <v>123</v>
+      </c>
+      <c r="F26" s="29">
+        <v>127</v>
+      </c>
+      <c r="G26" s="29">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="23">
+        <v>46042</v>
+      </c>
+      <c r="B27" s="23">
+        <v>46042</v>
+      </c>
+      <c r="C27" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" s="29">
+        <v>158</v>
+      </c>
+      <c r="F27" s="29">
+        <v>162</v>
+      </c>
+      <c r="G27" s="29">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="23">
+        <v>46049</v>
+      </c>
+      <c r="B28" s="23">
+        <v>46049</v>
+      </c>
+      <c r="C28" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="30">
+        <v>168</v>
+      </c>
+      <c r="F28" s="30">
+        <v>172</v>
+      </c>
+      <c r="G28" s="30">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="23">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="23">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="30">
+        <v>168</v>
+      </c>
+      <c r="F29" s="30">
+        <v>172</v>
+      </c>
+      <c r="G29" s="30">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="23">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="23">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="30">
+        <v>168</v>
+      </c>
+      <c r="F30" s="30">
+        <v>172</v>
+      </c>
+      <c r="G30" s="30">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="23">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="23">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="30">
+        <v>168</v>
+      </c>
+      <c r="F31" s="30">
+        <v>172</v>
+      </c>
+      <c r="G31" s="30">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="23">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="23">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="30">
+        <v>168</v>
+      </c>
+      <c r="F32" s="30">
+        <v>172</v>
+      </c>
+      <c r="G32" s="30">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="23">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="23">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="30">
+        <v>188</v>
+      </c>
+      <c r="F33" s="30">
+        <v>192</v>
+      </c>
+      <c r="G33" s="30">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="23">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="23">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="24">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="30">
+        <v>188</v>
+      </c>
+      <c r="F34" s="30">
+        <v>192</v>
+      </c>
+      <c r="G34" s="30">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="23">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="23">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="24">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="30">
+        <v>188</v>
+      </c>
+      <c r="F35" s="30">
+        <v>192</v>
+      </c>
+      <c r="G35" s="30">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="23">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="23">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="24">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D36" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="30">
+        <v>168</v>
+      </c>
+      <c r="F36" s="30">
+        <v>172</v>
+      </c>
+      <c r="G36" s="30">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="23">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="23">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="24">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D37" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="30">
+        <v>168</v>
+      </c>
+      <c r="F37" s="30">
+        <v>172</v>
+      </c>
+      <c r="G37" s="30">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="23">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="23">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="24">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D38" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="30">
+        <v>163</v>
+      </c>
+      <c r="F38" s="30">
+        <v>167</v>
+      </c>
+      <c r="G38" s="30">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="23">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="23">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="24">
+        <v>0.45833333333333098</v>
+      </c>
+      <c r="D39" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="30">
+        <v>158</v>
+      </c>
+      <c r="F39" s="30">
+        <v>162</v>
+      </c>
+      <c r="G39" s="30">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="23">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="23">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="24">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D40" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="30">
+        <v>153</v>
+      </c>
+      <c r="F40" s="30">
         <v>157</v>
       </c>
-      <c r="F20" s="10">
-        <v>163</v>
-      </c>
-      <c r="G20" s="10">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="5">
-        <v>46000</v>
-      </c>
-      <c r="B21" s="5">
-        <v>46000</v>
-      </c>
-      <c r="C21" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E21" s="10">
-        <v>217</v>
-      </c>
-      <c r="F21" s="10">
-        <v>223</v>
-      </c>
-      <c r="G21" s="10">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="5">
-        <v>46007</v>
-      </c>
-      <c r="B22" s="5">
-        <v>46007</v>
-      </c>
-      <c r="C22" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22" s="10">
-        <v>217</v>
-      </c>
-      <c r="F22" s="10">
-        <v>223</v>
-      </c>
-      <c r="G22" s="10">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="5">
-        <v>46014</v>
-      </c>
-      <c r="B23" s="5">
-        <v>46014</v>
-      </c>
-      <c r="C23" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" s="10">
-        <v>217</v>
-      </c>
-      <c r="F23" s="10">
-        <v>223</v>
-      </c>
-      <c r="G23" s="10">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="5">
-        <v>46021</v>
-      </c>
-      <c r="B24" s="5">
-        <v>46021</v>
-      </c>
-      <c r="C24" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E24" s="10">
-        <v>217</v>
-      </c>
-      <c r="F24" s="10">
-        <v>223</v>
-      </c>
-      <c r="G24" s="10">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="5">
-        <v>46028</v>
-      </c>
-      <c r="B25" s="5">
-        <v>46028</v>
-      </c>
-      <c r="C25" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" s="10">
-        <v>227</v>
-      </c>
-      <c r="F25" s="10">
-        <v>233</v>
-      </c>
-      <c r="G25" s="10">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="8">
-        <v>46035</v>
-      </c>
-      <c r="B26" s="8">
-        <v>46035</v>
-      </c>
-      <c r="C26" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E26" s="10">
-        <v>227</v>
-      </c>
-      <c r="F26" s="10">
-        <v>233</v>
-      </c>
-      <c r="G26" s="10">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="8">
-        <v>46042</v>
-      </c>
-      <c r="B27" s="8">
-        <v>46042</v>
-      </c>
-      <c r="C27" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E27" s="10">
-        <v>257</v>
-      </c>
-      <c r="F27" s="10">
-        <v>263</v>
-      </c>
-      <c r="G27" s="10">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="8">
-        <v>46049</v>
-      </c>
-      <c r="B28" s="8">
-        <v>46049</v>
-      </c>
-      <c r="C28" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="11">
-        <v>267</v>
-      </c>
-      <c r="F28" s="11">
-        <v>273</v>
-      </c>
-      <c r="G28" s="11">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="8">
-        <v>46056</v>
-      </c>
-      <c r="B29" s="8">
-        <v>46056</v>
-      </c>
-      <c r="C29" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="11">
-        <v>267</v>
-      </c>
-      <c r="F29" s="11">
-        <v>273</v>
-      </c>
-      <c r="G29" s="11">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="8">
-        <v>46063</v>
-      </c>
-      <c r="B30" s="8">
-        <v>46063</v>
-      </c>
-      <c r="C30" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="11">
-        <v>267</v>
-      </c>
-      <c r="F30" s="11">
-        <v>273</v>
-      </c>
-      <c r="G30" s="11">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="8">
-        <v>46077</v>
-      </c>
-      <c r="B31" s="8">
-        <v>46077</v>
-      </c>
-      <c r="C31" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="11">
-        <v>267</v>
-      </c>
-      <c r="F31" s="11">
-        <v>273</v>
-      </c>
-      <c r="G31" s="11">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" s="8">
-        <v>46084</v>
-      </c>
-      <c r="B32" s="8">
-        <v>46084</v>
-      </c>
-      <c r="C32" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="11">
-        <v>267</v>
-      </c>
-      <c r="F32" s="11">
-        <v>273</v>
-      </c>
-      <c r="G32" s="11">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" s="8">
-        <v>46091</v>
-      </c>
-      <c r="B33" s="8">
-        <v>46091</v>
-      </c>
-      <c r="C33" s="6">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="11">
-        <v>317</v>
-      </c>
-      <c r="F33" s="11">
-        <v>323</v>
-      </c>
-      <c r="G33" s="11">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A34" s="8">
-        <v>46098</v>
-      </c>
-      <c r="B34" s="8">
-        <v>46098</v>
-      </c>
-      <c r="C34" s="6">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" s="11">
-        <v>317</v>
-      </c>
-      <c r="F34" s="11">
-        <v>323</v>
-      </c>
-      <c r="G34" s="11">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A35" s="8">
-        <v>46105</v>
-      </c>
-      <c r="B35" s="8">
-        <v>46105</v>
-      </c>
-      <c r="C35" s="6">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E35" s="11">
-        <v>317</v>
-      </c>
-      <c r="F35" s="11">
-        <v>323</v>
-      </c>
-      <c r="G35" s="11">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" s="8">
-        <v>46112</v>
-      </c>
-      <c r="B36" s="8">
-        <v>46112</v>
-      </c>
-      <c r="C36" s="6">
+      <c r="G40" s="30">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="23">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="23">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="24">
         <v>0.45833333333333198</v>
       </c>
-      <c r="D36" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E36" s="11">
-        <v>287</v>
-      </c>
-      <c r="F36" s="11">
-        <v>293</v>
-      </c>
-      <c r="G36" s="11">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A37" s="8">
-        <v>46119</v>
-      </c>
-      <c r="B37" s="8">
-        <v>46119</v>
-      </c>
-      <c r="C37" s="6">
+      <c r="D41" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="30">
+        <v>148</v>
+      </c>
+      <c r="F41" s="30">
+        <v>152</v>
+      </c>
+      <c r="G41" s="30">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="23">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="23">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="24">
         <v>0.45833333333333198</v>
       </c>
-      <c r="D37" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E37" s="11">
-        <v>287</v>
-      </c>
-      <c r="F37" s="11">
-        <v>293</v>
-      </c>
-      <c r="G37" s="11">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38" s="8">
-        <v>46126</v>
-      </c>
-      <c r="B38" s="8">
-        <v>46126</v>
-      </c>
-      <c r="C38" s="6">
+      <c r="D42" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="30">
+        <v>146</v>
+      </c>
+      <c r="F42" s="30">
+        <v>150</v>
+      </c>
+      <c r="G42" s="30">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="23">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="23">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="24">
         <v>0.45833333333333198</v>
       </c>
-      <c r="D38" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E38" s="11">
-        <v>277</v>
-      </c>
-      <c r="F38" s="11">
-        <v>283</v>
-      </c>
-      <c r="G38" s="11">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A39" s="8">
-        <v>46133</v>
-      </c>
-      <c r="B39" s="8">
-        <v>46133</v>
-      </c>
-      <c r="C39" s="6">
-        <v>0.45833333333333098</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E39" s="11">
-        <v>272</v>
-      </c>
-      <c r="F39" s="11">
-        <v>278</v>
-      </c>
-      <c r="G39" s="11">
-        <v>275</v>
+      <c r="D43" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="30">
+        <v>146</v>
+      </c>
+      <c r="F43" s="30">
+        <v>150</v>
+      </c>
+      <c r="G43" s="30">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="23">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="23">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="24">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D44" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="30">
+        <v>146</v>
+      </c>
+      <c r="F44" s="30">
+        <v>150</v>
+      </c>
+      <c r="G44" s="30">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="23">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="23">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="24">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D45" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="30">
+        <v>147</v>
+      </c>
+      <c r="F45" s="30">
+        <v>151</v>
+      </c>
+      <c r="G45" s="30">
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -5966,21 +4995,20 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D2BE078-281B-4EE8-A7DD-0530E85C5130}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55494817-78A6-45DF-9F77-86066DAB20E2}">
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.69921875" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="11.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" style="17"/>
+    <col min="7" max="7" width="11.21875" style="17" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5993,6 +5021,1061 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="5">
+        <v>45860</v>
+      </c>
+      <c r="B2" s="5">
+        <v>45860</v>
+      </c>
+      <c r="C2" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="16">
+        <v>33</v>
+      </c>
+      <c r="F2" s="16">
+        <v>37</v>
+      </c>
+      <c r="G2" s="16">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="5">
+        <v>45867</v>
+      </c>
+      <c r="B3" s="5">
+        <v>45867</v>
+      </c>
+      <c r="C3" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="16">
+        <v>33</v>
+      </c>
+      <c r="F3" s="16">
+        <v>37</v>
+      </c>
+      <c r="G3" s="16">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="5">
+        <v>45874</v>
+      </c>
+      <c r="B4" s="5">
+        <v>45874</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="16">
+        <v>33</v>
+      </c>
+      <c r="F4" s="16">
+        <v>37</v>
+      </c>
+      <c r="G4" s="16">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="5">
+        <v>45881</v>
+      </c>
+      <c r="B5" s="5">
+        <v>45881</v>
+      </c>
+      <c r="C5" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="16">
+        <v>33</v>
+      </c>
+      <c r="F5" s="16">
+        <v>37</v>
+      </c>
+      <c r="G5" s="16">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="5">
+        <v>45888</v>
+      </c>
+      <c r="B6" s="5">
+        <v>45888</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="16">
+        <v>33</v>
+      </c>
+      <c r="F6" s="16">
+        <v>37</v>
+      </c>
+      <c r="G6" s="16">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="5">
+        <v>45895</v>
+      </c>
+      <c r="B7" s="5">
+        <v>45895</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="16">
+        <v>34</v>
+      </c>
+      <c r="F7" s="16">
+        <v>38</v>
+      </c>
+      <c r="G7" s="16">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="5">
+        <v>45902</v>
+      </c>
+      <c r="B8" s="5">
+        <v>45902</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="16">
+        <v>35</v>
+      </c>
+      <c r="F8" s="16">
+        <v>39</v>
+      </c>
+      <c r="G8" s="16">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="5">
+        <v>45909</v>
+      </c>
+      <c r="B9" s="5">
+        <v>45909</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="16">
+        <v>35.4</v>
+      </c>
+      <c r="F9" s="16">
+        <v>39.4</v>
+      </c>
+      <c r="G9" s="16">
+        <v>37.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="5">
+        <v>45916</v>
+      </c>
+      <c r="B10" s="5">
+        <v>45916</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="16">
+        <v>36</v>
+      </c>
+      <c r="F10" s="16">
+        <v>40</v>
+      </c>
+      <c r="G10" s="16">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="5">
+        <v>45923</v>
+      </c>
+      <c r="B11" s="5">
+        <v>45923</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="16">
+        <v>36</v>
+      </c>
+      <c r="F11" s="16">
+        <v>40</v>
+      </c>
+      <c r="G11" s="16">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="5">
+        <v>45930</v>
+      </c>
+      <c r="B12" s="5">
+        <v>45930</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="16">
+        <v>36</v>
+      </c>
+      <c r="F12" s="16">
+        <v>40</v>
+      </c>
+      <c r="G12" s="16">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="5">
+        <v>45944</v>
+      </c>
+      <c r="B13" s="5">
+        <v>45944</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="16">
+        <v>43</v>
+      </c>
+      <c r="F13" s="16">
+        <v>47</v>
+      </c>
+      <c r="G13" s="16">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="5">
+        <v>45951</v>
+      </c>
+      <c r="B14" s="5">
+        <v>45951</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="16">
+        <v>43</v>
+      </c>
+      <c r="F14" s="16">
+        <v>47</v>
+      </c>
+      <c r="G14" s="16">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="5">
+        <v>45958</v>
+      </c>
+      <c r="B15" s="5">
+        <v>45958</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="16">
+        <v>43</v>
+      </c>
+      <c r="F15" s="16">
+        <v>47</v>
+      </c>
+      <c r="G15" s="16">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="5">
+        <v>45965</v>
+      </c>
+      <c r="B16" s="5">
+        <v>45965</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="16">
+        <v>43</v>
+      </c>
+      <c r="F16" s="16">
+        <v>47</v>
+      </c>
+      <c r="G16" s="16">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="5">
+        <v>45972</v>
+      </c>
+      <c r="B17" s="5">
+        <v>45972</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="16">
+        <v>43</v>
+      </c>
+      <c r="F17" s="16">
+        <v>47</v>
+      </c>
+      <c r="G17" s="16">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="5">
+        <v>45979</v>
+      </c>
+      <c r="B18" s="5">
+        <v>45979</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="16">
+        <v>43</v>
+      </c>
+      <c r="F18" s="16">
+        <v>47</v>
+      </c>
+      <c r="G18" s="16">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="5">
+        <v>45986</v>
+      </c>
+      <c r="B19" s="5">
+        <v>45986</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="16">
+        <v>63</v>
+      </c>
+      <c r="F19" s="16">
+        <v>67</v>
+      </c>
+      <c r="G19" s="16">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="5">
+        <v>45993</v>
+      </c>
+      <c r="B20" s="5">
+        <v>45993</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="16">
+        <v>88</v>
+      </c>
+      <c r="F20" s="16">
+        <v>92</v>
+      </c>
+      <c r="G20" s="16">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="5">
+        <v>46000</v>
+      </c>
+      <c r="B21" s="5">
+        <v>46000</v>
+      </c>
+      <c r="C21" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="16">
+        <v>118</v>
+      </c>
+      <c r="F21" s="16">
+        <v>122</v>
+      </c>
+      <c r="G21" s="16">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="5">
+        <v>46007</v>
+      </c>
+      <c r="B22" s="5">
+        <v>46007</v>
+      </c>
+      <c r="C22" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="16">
+        <v>118</v>
+      </c>
+      <c r="F22" s="16">
+        <v>122</v>
+      </c>
+      <c r="G22" s="16">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="5">
+        <v>46014</v>
+      </c>
+      <c r="B23" s="5">
+        <v>46014</v>
+      </c>
+      <c r="C23" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="16">
+        <v>118</v>
+      </c>
+      <c r="F23" s="16">
+        <v>122</v>
+      </c>
+      <c r="G23" s="16">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="5">
+        <v>46021</v>
+      </c>
+      <c r="B24" s="5">
+        <v>46021</v>
+      </c>
+      <c r="C24" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="16">
+        <v>118</v>
+      </c>
+      <c r="F24" s="16">
+        <v>122</v>
+      </c>
+      <c r="G24" s="16">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="5">
+        <v>46028</v>
+      </c>
+      <c r="B25" s="5">
+        <v>46028</v>
+      </c>
+      <c r="C25" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="16">
+        <v>143</v>
+      </c>
+      <c r="F25" s="16">
+        <v>147</v>
+      </c>
+      <c r="G25" s="16">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="8">
+        <v>46035</v>
+      </c>
+      <c r="B26" s="8">
+        <v>46035</v>
+      </c>
+      <c r="C26" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="16">
+        <v>143</v>
+      </c>
+      <c r="F26" s="16">
+        <v>147</v>
+      </c>
+      <c r="G26" s="16">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="8">
+        <v>46042</v>
+      </c>
+      <c r="B27" s="8">
+        <v>46042</v>
+      </c>
+      <c r="C27" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" s="16">
+        <v>167</v>
+      </c>
+      <c r="F27" s="16">
+        <v>172</v>
+      </c>
+      <c r="G27" s="16">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="8">
+        <v>46049</v>
+      </c>
+      <c r="B28" s="8">
+        <v>46049</v>
+      </c>
+      <c r="C28" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="17">
+        <v>177</v>
+      </c>
+      <c r="F28" s="17">
+        <v>182</v>
+      </c>
+      <c r="G28" s="17">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="17">
+        <v>177</v>
+      </c>
+      <c r="F29" s="17">
+        <v>182</v>
+      </c>
+      <c r="G29" s="17">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="17">
+        <v>177</v>
+      </c>
+      <c r="F30" s="17">
+        <v>182</v>
+      </c>
+      <c r="G30" s="17">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="17">
+        <v>177</v>
+      </c>
+      <c r="F31" s="17">
+        <v>182</v>
+      </c>
+      <c r="G31" s="17">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="17">
+        <v>177</v>
+      </c>
+      <c r="F32" s="17">
+        <v>182</v>
+      </c>
+      <c r="G32" s="17">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="17">
+        <v>197</v>
+      </c>
+      <c r="F33" s="17">
+        <v>202</v>
+      </c>
+      <c r="G33" s="17">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="8">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="8">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="17">
+        <v>197</v>
+      </c>
+      <c r="F34" s="17">
+        <v>202</v>
+      </c>
+      <c r="G34" s="17">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="8">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="8">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="17">
+        <v>197</v>
+      </c>
+      <c r="F35" s="17">
+        <v>202</v>
+      </c>
+      <c r="G35" s="17">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="8">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="8">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="17">
+        <v>177</v>
+      </c>
+      <c r="F36" s="17">
+        <v>182</v>
+      </c>
+      <c r="G36" s="17">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="8">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="8">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="17">
+        <v>177</v>
+      </c>
+      <c r="F37" s="17">
+        <v>182</v>
+      </c>
+      <c r="G37" s="17">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="8">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="8">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="17">
+        <v>167</v>
+      </c>
+      <c r="F38" s="17">
+        <v>172</v>
+      </c>
+      <c r="G38" s="17">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="8">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="8">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="6">
+        <v>0.45833333333333098</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="17">
+        <v>164</v>
+      </c>
+      <c r="F39" s="17">
+        <v>169</v>
+      </c>
+      <c r="G39" s="17">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="17">
+        <v>164</v>
+      </c>
+      <c r="F40" s="17">
+        <v>169</v>
+      </c>
+      <c r="G40" s="17">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="17">
+        <v>157</v>
+      </c>
+      <c r="F41" s="17">
+        <v>162</v>
+      </c>
+      <c r="G41" s="17">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="17">
+        <v>149</v>
+      </c>
+      <c r="F42" s="17">
+        <v>154</v>
+      </c>
+      <c r="G42" s="17">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="17">
+        <v>149</v>
+      </c>
+      <c r="F43" s="17">
+        <v>154</v>
+      </c>
+      <c r="G43" s="17">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="17">
+        <v>149</v>
+      </c>
+      <c r="F44" s="17">
+        <v>154</v>
+      </c>
+      <c r="G44" s="17">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="17">
+        <v>150</v>
+      </c>
+      <c r="F45" s="17">
+        <v>155</v>
+      </c>
+      <c r="G45" s="17">
+        <v>153</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B6A378-E9BB-4F97-B1F3-B76BB8A3CEFF}">
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <cols>
+    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" style="11"/>
+    <col min="7" max="7" width="11.21875" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="E1" s="9" t="s">
         <v>5</v>
       </c>
@@ -6003,7 +6086,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="5">
         <v>45860</v>
       </c>
@@ -6017,6 +6100,1062 @@
         <v>7</v>
       </c>
       <c r="E2" s="10">
+        <v>62</v>
+      </c>
+      <c r="F2" s="10">
+        <v>68</v>
+      </c>
+      <c r="G2" s="10">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="5">
+        <v>45867</v>
+      </c>
+      <c r="B3" s="5">
+        <v>45867</v>
+      </c>
+      <c r="C3" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="10">
+        <v>62</v>
+      </c>
+      <c r="F3" s="10">
+        <v>68</v>
+      </c>
+      <c r="G3" s="10">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="5">
+        <v>45874</v>
+      </c>
+      <c r="B4" s="5">
+        <v>45874</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="10">
+        <v>62</v>
+      </c>
+      <c r="F4" s="10">
+        <v>68</v>
+      </c>
+      <c r="G4" s="10">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="5">
+        <v>45881</v>
+      </c>
+      <c r="B5" s="5">
+        <v>45881</v>
+      </c>
+      <c r="C5" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="10">
+        <v>62</v>
+      </c>
+      <c r="F5" s="10">
+        <v>68</v>
+      </c>
+      <c r="G5" s="10">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="5">
+        <v>45888</v>
+      </c>
+      <c r="B6" s="5">
+        <v>45888</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="10">
+        <v>62</v>
+      </c>
+      <c r="F6" s="10">
+        <v>68</v>
+      </c>
+      <c r="G6" s="10">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="5">
+        <v>45895</v>
+      </c>
+      <c r="B7" s="5">
+        <v>45895</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="10">
+        <v>63</v>
+      </c>
+      <c r="F7" s="10">
+        <v>69</v>
+      </c>
+      <c r="G7" s="10">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="5">
+        <v>45902</v>
+      </c>
+      <c r="B8" s="5">
+        <v>45902</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="10">
+        <v>65</v>
+      </c>
+      <c r="F8" s="10">
+        <v>71</v>
+      </c>
+      <c r="G8" s="10">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="5">
+        <v>45909</v>
+      </c>
+      <c r="B9" s="5">
+        <v>45909</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="10">
+        <v>65.5</v>
+      </c>
+      <c r="F9" s="10">
+        <v>71.5</v>
+      </c>
+      <c r="G9" s="10">
+        <v>68.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="5">
+        <v>45916</v>
+      </c>
+      <c r="B10" s="5">
+        <v>45916</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="10">
+        <v>66.2</v>
+      </c>
+      <c r="F10" s="10">
+        <v>72.2</v>
+      </c>
+      <c r="G10" s="10">
+        <v>69.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="5">
+        <v>45923</v>
+      </c>
+      <c r="B11" s="5">
+        <v>45923</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="10">
+        <v>66.2</v>
+      </c>
+      <c r="F11" s="10">
+        <v>72.2</v>
+      </c>
+      <c r="G11" s="10">
+        <v>69.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="5">
+        <v>45930</v>
+      </c>
+      <c r="B12" s="5">
+        <v>45930</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="10">
+        <v>66.2</v>
+      </c>
+      <c r="F12" s="10">
+        <v>72.2</v>
+      </c>
+      <c r="G12" s="10">
+        <v>69.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="5">
+        <v>45944</v>
+      </c>
+      <c r="B13" s="5">
+        <v>45944</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="10">
+        <v>79</v>
+      </c>
+      <c r="F13" s="10">
+        <v>85</v>
+      </c>
+      <c r="G13" s="10">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="5">
+        <v>45951</v>
+      </c>
+      <c r="B14" s="5">
+        <v>45951</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="10">
+        <v>79</v>
+      </c>
+      <c r="F14" s="10">
+        <v>85</v>
+      </c>
+      <c r="G14" s="10">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="5">
+        <v>45958</v>
+      </c>
+      <c r="B15" s="5">
+        <v>45958</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="10">
+        <v>79</v>
+      </c>
+      <c r="F15" s="10">
+        <v>85</v>
+      </c>
+      <c r="G15" s="10">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="5">
+        <v>45965</v>
+      </c>
+      <c r="B16" s="5">
+        <v>45965</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="10">
+        <v>79</v>
+      </c>
+      <c r="F16" s="10">
+        <v>85</v>
+      </c>
+      <c r="G16" s="10">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="5">
+        <v>45972</v>
+      </c>
+      <c r="B17" s="5">
+        <v>45972</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="10">
+        <v>79</v>
+      </c>
+      <c r="F17" s="10">
+        <v>85</v>
+      </c>
+      <c r="G17" s="10">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="5">
+        <v>45979</v>
+      </c>
+      <c r="B18" s="5">
+        <v>45979</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="10">
+        <v>79</v>
+      </c>
+      <c r="F18" s="10">
+        <v>85</v>
+      </c>
+      <c r="G18" s="10">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="5">
+        <v>45986</v>
+      </c>
+      <c r="B19" s="5">
+        <v>45986</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="10">
+        <v>114</v>
+      </c>
+      <c r="F19" s="10">
+        <v>120</v>
+      </c>
+      <c r="G19" s="10">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="5">
+        <v>45993</v>
+      </c>
+      <c r="B20" s="5">
+        <v>45993</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="10">
+        <v>157</v>
+      </c>
+      <c r="F20" s="10">
+        <v>163</v>
+      </c>
+      <c r="G20" s="10">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="5">
+        <v>46000</v>
+      </c>
+      <c r="B21" s="5">
+        <v>46000</v>
+      </c>
+      <c r="C21" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="10">
+        <v>217</v>
+      </c>
+      <c r="F21" s="10">
+        <v>223</v>
+      </c>
+      <c r="G21" s="10">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="5">
+        <v>46007</v>
+      </c>
+      <c r="B22" s="5">
+        <v>46007</v>
+      </c>
+      <c r="C22" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="10">
+        <v>217</v>
+      </c>
+      <c r="F22" s="10">
+        <v>223</v>
+      </c>
+      <c r="G22" s="10">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="5">
+        <v>46014</v>
+      </c>
+      <c r="B23" s="5">
+        <v>46014</v>
+      </c>
+      <c r="C23" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="10">
+        <v>217</v>
+      </c>
+      <c r="F23" s="10">
+        <v>223</v>
+      </c>
+      <c r="G23" s="10">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="5">
+        <v>46021</v>
+      </c>
+      <c r="B24" s="5">
+        <v>46021</v>
+      </c>
+      <c r="C24" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="10">
+        <v>217</v>
+      </c>
+      <c r="F24" s="10">
+        <v>223</v>
+      </c>
+      <c r="G24" s="10">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="5">
+        <v>46028</v>
+      </c>
+      <c r="B25" s="5">
+        <v>46028</v>
+      </c>
+      <c r="C25" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="10">
+        <v>227</v>
+      </c>
+      <c r="F25" s="10">
+        <v>233</v>
+      </c>
+      <c r="G25" s="10">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="8">
+        <v>46035</v>
+      </c>
+      <c r="B26" s="8">
+        <v>46035</v>
+      </c>
+      <c r="C26" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="10">
+        <v>227</v>
+      </c>
+      <c r="F26" s="10">
+        <v>233</v>
+      </c>
+      <c r="G26" s="10">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="8">
+        <v>46042</v>
+      </c>
+      <c r="B27" s="8">
+        <v>46042</v>
+      </c>
+      <c r="C27" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" s="10">
+        <v>257</v>
+      </c>
+      <c r="F27" s="10">
+        <v>263</v>
+      </c>
+      <c r="G27" s="10">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="8">
+        <v>46049</v>
+      </c>
+      <c r="B28" s="8">
+        <v>46049</v>
+      </c>
+      <c r="C28" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="11">
+        <v>267</v>
+      </c>
+      <c r="F28" s="11">
+        <v>273</v>
+      </c>
+      <c r="G28" s="11">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="11">
+        <v>267</v>
+      </c>
+      <c r="F29" s="11">
+        <v>273</v>
+      </c>
+      <c r="G29" s="11">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="11">
+        <v>267</v>
+      </c>
+      <c r="F30" s="11">
+        <v>273</v>
+      </c>
+      <c r="G30" s="11">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="11">
+        <v>267</v>
+      </c>
+      <c r="F31" s="11">
+        <v>273</v>
+      </c>
+      <c r="G31" s="11">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="11">
+        <v>267</v>
+      </c>
+      <c r="F32" s="11">
+        <v>273</v>
+      </c>
+      <c r="G32" s="11">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="11">
+        <v>317</v>
+      </c>
+      <c r="F33" s="11">
+        <v>323</v>
+      </c>
+      <c r="G33" s="11">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="8">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="8">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="11">
+        <v>317</v>
+      </c>
+      <c r="F34" s="11">
+        <v>323</v>
+      </c>
+      <c r="G34" s="11">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="8">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="8">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="11">
+        <v>317</v>
+      </c>
+      <c r="F35" s="11">
+        <v>323</v>
+      </c>
+      <c r="G35" s="11">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="8">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="8">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="11">
+        <v>287</v>
+      </c>
+      <c r="F36" s="11">
+        <v>293</v>
+      </c>
+      <c r="G36" s="11">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="8">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="8">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="11">
+        <v>287</v>
+      </c>
+      <c r="F37" s="11">
+        <v>293</v>
+      </c>
+      <c r="G37" s="11">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="8">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="8">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="11">
+        <v>277</v>
+      </c>
+      <c r="F38" s="11">
+        <v>283</v>
+      </c>
+      <c r="G38" s="11">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="8">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="8">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="6">
+        <v>0.45833333333333098</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="11">
+        <v>272</v>
+      </c>
+      <c r="F39" s="11">
+        <v>278</v>
+      </c>
+      <c r="G39" s="11">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="11">
+        <v>267</v>
+      </c>
+      <c r="F40" s="11">
+        <v>273</v>
+      </c>
+      <c r="G40" s="11">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="11">
+        <v>257</v>
+      </c>
+      <c r="F41" s="11">
+        <v>263</v>
+      </c>
+      <c r="G41" s="11">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="11">
+        <v>252</v>
+      </c>
+      <c r="F42" s="11">
+        <v>258</v>
+      </c>
+      <c r="G42" s="11">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="11">
+        <v>252</v>
+      </c>
+      <c r="F43" s="11">
+        <v>258</v>
+      </c>
+      <c r="G43" s="11">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="11">
+        <v>252</v>
+      </c>
+      <c r="F44" s="11">
+        <v>258</v>
+      </c>
+      <c r="G44" s="11">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="11">
+        <v>252</v>
+      </c>
+      <c r="F45" s="11">
+        <v>258</v>
+      </c>
+      <c r="G45" s="11">
+        <v>255</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D2BE078-281B-4EE8-A7DD-0530E85C5130}">
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <cols>
+    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" style="11"/>
+    <col min="7" max="7" width="11.21875" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="5">
+        <v>45860</v>
+      </c>
+      <c r="B2" s="5">
+        <v>45860</v>
+      </c>
+      <c r="C2" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="10">
         <v>64</v>
       </c>
       <c r="F2" s="10">
@@ -6026,7 +7165,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="5">
         <v>45867</v>
       </c>
@@ -6049,7 +7188,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="5">
         <v>45874</v>
       </c>
@@ -6072,7 +7211,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="5">
         <v>45881</v>
       </c>
@@ -6095,7 +7234,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="5">
         <v>45888</v>
       </c>
@@ -6118,7 +7257,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="5">
         <v>45895</v>
       </c>
@@ -6141,7 +7280,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="5">
         <v>45902</v>
       </c>
@@ -6164,7 +7303,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="5">
         <v>45909</v>
       </c>
@@ -6187,7 +7326,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="5">
         <v>45916</v>
       </c>
@@ -6210,7 +7349,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="5">
         <v>45923</v>
       </c>
@@ -6233,7 +7372,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="5">
         <v>45930</v>
       </c>
@@ -6256,7 +7395,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="5">
         <v>45944</v>
       </c>
@@ -6279,7 +7418,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="5">
         <v>45951</v>
       </c>
@@ -6302,7 +7441,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="5">
         <v>45958</v>
       </c>
@@ -6325,7 +7464,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="5">
         <v>45965</v>
       </c>
@@ -6348,7 +7487,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="5">
         <v>45972</v>
       </c>
@@ -6371,7 +7510,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="5">
         <v>45979</v>
       </c>
@@ -6394,7 +7533,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="5">
         <v>45986</v>
       </c>
@@ -6417,7 +7556,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="5">
         <v>45993</v>
       </c>
@@ -6440,7 +7579,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="5">
         <v>46000</v>
       </c>
@@ -6463,7 +7602,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="5">
         <v>46007</v>
       </c>
@@ -6486,7 +7625,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="5">
         <v>46014</v>
       </c>
@@ -6509,7 +7648,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="5">
         <v>46021</v>
       </c>
@@ -6532,7 +7671,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="5">
         <v>46028</v>
       </c>
@@ -6555,7 +7694,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="8">
         <v>46035</v>
       </c>
@@ -6578,7 +7717,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="8">
         <v>46042</v>
       </c>
@@ -6601,7 +7740,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="8">
         <v>46049</v>
       </c>
@@ -6624,7 +7763,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="8">
         <v>46056</v>
       </c>
@@ -6647,7 +7786,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="8">
         <v>46063</v>
       </c>
@@ -6670,7 +7809,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="8">
         <v>46077</v>
       </c>
@@ -6693,7 +7832,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="8">
         <v>46084</v>
       </c>
@@ -6716,7 +7855,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="8">
         <v>46091</v>
       </c>
@@ -6739,7 +7878,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="8">
         <v>46098</v>
       </c>
@@ -6762,7 +7901,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="8">
         <v>46105</v>
       </c>
@@ -6785,7 +7924,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="8">
         <v>46112</v>
       </c>
@@ -6808,7 +7947,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="8">
         <v>46119</v>
       </c>
@@ -6831,7 +7970,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="8">
         <v>46126</v>
       </c>
@@ -6854,7 +7993,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="8">
         <v>46133</v>
       </c>
@@ -6875,6 +8014,144 @@
       </c>
       <c r="G39" s="11">
         <v>280</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="11">
+        <v>272</v>
+      </c>
+      <c r="F40" s="11">
+        <v>278</v>
+      </c>
+      <c r="G40" s="11">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="11">
+        <v>267</v>
+      </c>
+      <c r="F41" s="11">
+        <v>273</v>
+      </c>
+      <c r="G41" s="11">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="11">
+        <v>262</v>
+      </c>
+      <c r="F42" s="11">
+        <v>268</v>
+      </c>
+      <c r="G42" s="11">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="11">
+        <v>262</v>
+      </c>
+      <c r="F43" s="11">
+        <v>268</v>
+      </c>
+      <c r="G43" s="11">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="11">
+        <v>262</v>
+      </c>
+      <c r="F44" s="11">
+        <v>268</v>
+      </c>
+      <c r="G44" s="11">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="6">
+        <v>0.45833333333333198</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="11">
+        <v>262</v>
+      </c>
+      <c r="F45" s="11">
+        <v>268</v>
+      </c>
+      <c r="G45" s="11">
+        <v>265</v>
       </c>
     </row>
   </sheetData>
